--- a/data/GBD_diseases.xlsx
+++ b/data/GBD_diseases.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ines/Documents/PhD/PROJETS/MARCHE/HIA_walking_steps/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF4D7074-3993-FF4A-8B8E-CE2570A8A7F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52FC59B4-F6E9-C843-B2C1-D8874C9597A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="880" yWindow="500" windowWidth="27920" windowHeight="16100" activeTab="2" xr2:uid="{E681AD37-9457-C84A-B54A-A4A5BA37FC49}"/>
+    <workbookView xWindow="33860" yWindow="-1020" windowWidth="27920" windowHeight="16100" activeTab="2" xr2:uid="{E681AD37-9457-C84A-B54A-A4A5BA37FC49}"/>
   </bookViews>
   <sheets>
     <sheet name="Central" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="33">
   <si>
     <t>Male</t>
   </si>
@@ -119,6 +119,24 @@
   </si>
   <si>
     <t>cc_incidence</t>
+  </si>
+  <si>
+    <t>bc_prevalence</t>
+  </si>
+  <si>
+    <t>cc_prevalence</t>
+  </si>
+  <si>
+    <t>cvd_prevalence</t>
+  </si>
+  <si>
+    <t>cancer_prevalence</t>
+  </si>
+  <si>
+    <t>diab2_prevalence</t>
+  </si>
+  <si>
+    <t>dem_prevalence</t>
   </si>
 </sst>
 </file>
@@ -499,20 +517,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDD0F75B-B6CB-6D48-ABCA-C0DE307A97B8}">
-  <dimension ref="A1:K29"/>
+  <dimension ref="A1:Q29"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="4" max="4" width="11.5" customWidth="1"/>
-    <col min="5" max="5" width="12" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.83203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.5" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.5" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.83203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.83203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16.83203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.5" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.5" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>23</v>
       </c>
@@ -526,28 +550,46 @@
         <v>25</v>
       </c>
       <c r="E1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" t="s">
         <v>26</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H1" t="s">
         <v>19</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
+        <v>29</v>
+      </c>
+      <c r="J1" t="s">
         <v>17</v>
       </c>
-      <c r="H1" t="s">
+      <c r="K1" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1" t="s">
         <v>18</v>
       </c>
-      <c r="I1" t="s">
+      <c r="M1" t="s">
+        <v>31</v>
+      </c>
+      <c r="N1" t="s">
         <v>20</v>
       </c>
-      <c r="J1" t="s">
+      <c r="O1" t="s">
+        <v>32</v>
+      </c>
+      <c r="P1" t="s">
         <v>16</v>
       </c>
-      <c r="K1" t="s">
+      <c r="Q1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -561,28 +603,46 @@
         <v>46.985244064993502</v>
       </c>
       <c r="E2" s="1">
+        <v>411.934552971014</v>
+      </c>
+      <c r="F2" s="1">
         <v>30.180880144163499</v>
       </c>
-      <c r="F2" s="2">
+      <c r="G2" s="1">
+        <v>229.85124684613399</v>
+      </c>
+      <c r="H2" s="2">
         <v>470.69469038044798</v>
       </c>
-      <c r="G2" s="1">
-        <v>31895.028700513602</v>
-      </c>
-      <c r="H2" s="1">
+      <c r="I2" s="1">
+        <v>22279.135448452402</v>
+      </c>
+      <c r="J2" s="2">
+        <v>723.30546376223401</v>
+      </c>
+      <c r="K2" s="1">
+        <v>5178.2833176166396</v>
+      </c>
+      <c r="L2" s="1">
         <v>1820.60209060134</v>
       </c>
-      <c r="I2" s="1">
-        <v>0</v>
-      </c>
-      <c r="J2" s="1">
+      <c r="M2" s="1">
+        <v>10388.0715849237</v>
+      </c>
+      <c r="N2" s="1">
+        <v>0</v>
+      </c>
+      <c r="O2" s="1">
+        <v>0</v>
+      </c>
+      <c r="P2" s="1">
         <v>110106.980466972</v>
       </c>
-      <c r="K2" s="1">
+      <c r="Q2" s="1">
         <v>67784.402232364999</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -596,28 +656,46 @@
         <v>262.93937582697203</v>
       </c>
       <c r="E3" s="1">
+        <v>2303.5176672724901</v>
+      </c>
+      <c r="F3" s="1">
         <v>51.168487926524399</v>
       </c>
-      <c r="F3" s="2">
+      <c r="G3" s="1">
+        <v>390.68419654643702</v>
+      </c>
+      <c r="H3" s="2">
         <v>632.77539815350804</v>
       </c>
-      <c r="G3" s="1">
-        <v>41373.529924294002</v>
-      </c>
-      <c r="H3" s="1">
+      <c r="I3" s="1">
+        <v>33279.702148941797</v>
+      </c>
+      <c r="J3" s="2">
+        <v>1375.75650737057</v>
+      </c>
+      <c r="K3" s="1">
+        <v>10137.3450912385</v>
+      </c>
+      <c r="L3" s="1">
         <v>2169.7299767801601</v>
       </c>
-      <c r="I3" s="1">
-        <v>0</v>
-      </c>
-      <c r="J3" s="1">
+      <c r="M3" s="1">
+        <v>22274.173198373599</v>
+      </c>
+      <c r="N3" s="1">
+        <v>0</v>
+      </c>
+      <c r="O3" s="1">
+        <v>0</v>
+      </c>
+      <c r="P3" s="1">
         <v>109941.189467854</v>
       </c>
-      <c r="K3" s="1">
+      <c r="Q3" s="1">
         <v>68455.523531892293</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -631,28 +709,46 @@
         <v>910.86506240088602</v>
       </c>
       <c r="E4" s="1">
+        <v>8023.7515821181296</v>
+      </c>
+      <c r="F4" s="1">
         <v>118.93048707633901</v>
       </c>
-      <c r="F4" s="2">
+      <c r="G4" s="1">
+        <v>911.53257665978504</v>
+      </c>
+      <c r="H4" s="2">
         <v>940.43433537620399</v>
       </c>
-      <c r="G4" s="1">
-        <v>54827.829429694502</v>
-      </c>
-      <c r="H4" s="1">
+      <c r="I4" s="1">
+        <v>52966.712990431697</v>
+      </c>
+      <c r="J4" s="2">
+        <v>2848.2396607588398</v>
+      </c>
+      <c r="K4" s="1">
+        <v>21322.376168045299</v>
+      </c>
+      <c r="L4" s="1">
         <v>2650.1162851320801</v>
       </c>
-      <c r="I4" s="1">
-        <v>0</v>
-      </c>
-      <c r="J4" s="1">
+      <c r="M4" s="1">
+        <v>37038.911890139199</v>
+      </c>
+      <c r="N4" s="1">
+        <v>0</v>
+      </c>
+      <c r="O4" s="1">
+        <v>0</v>
+      </c>
+      <c r="P4" s="1">
         <v>115456.646754588</v>
       </c>
-      <c r="K4" s="1">
+      <c r="Q4" s="1">
         <v>71858.1892132434</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>11</v>
       </c>
@@ -666,28 +762,46 @@
         <v>1869.5575392528101</v>
       </c>
       <c r="E5" s="1">
+        <v>16685.9072124021</v>
+      </c>
+      <c r="F5" s="1">
         <v>221.81545648879501</v>
       </c>
-      <c r="F5" s="2">
+      <c r="G5" s="1">
+        <v>1702.9490706071499</v>
+      </c>
+      <c r="H5" s="2">
         <v>1349.06519303611</v>
       </c>
-      <c r="G5" s="1">
-        <v>67646.912270110799</v>
-      </c>
-      <c r="H5" s="1">
+      <c r="I5" s="1">
+        <v>70192.947805836695</v>
+      </c>
+      <c r="J5" s="2">
+        <v>4940.8091841732203</v>
+      </c>
+      <c r="K5" s="1">
+        <v>36737.774399732603</v>
+      </c>
+      <c r="L5" s="1">
         <v>3193.72590896884</v>
       </c>
-      <c r="I5" s="1">
-        <v>0</v>
-      </c>
-      <c r="J5" s="1">
+      <c r="M5" s="1">
+        <v>52720.934337644001</v>
+      </c>
+      <c r="N5" s="1">
+        <v>0</v>
+      </c>
+      <c r="O5" s="1">
+        <v>0</v>
+      </c>
+      <c r="P5" s="1">
         <v>117815.618668783</v>
       </c>
-      <c r="K5" s="1">
+      <c r="Q5" s="1">
         <v>74423.611475318394</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -701,28 +815,46 @@
         <v>3605.9935562933301</v>
       </c>
       <c r="E6" s="1">
+        <v>32643.586856381098</v>
+      </c>
+      <c r="F6" s="1">
         <v>386.46161229705501</v>
       </c>
-      <c r="F6" s="2">
+      <c r="G6" s="1">
+        <v>2930.8673517757702</v>
+      </c>
+      <c r="H6" s="2">
         <v>3101.65917634979</v>
       </c>
-      <c r="G6" s="1">
-        <v>78426.804447342205</v>
-      </c>
-      <c r="H6" s="1">
+      <c r="I6" s="1">
+        <v>123457.905695632</v>
+      </c>
+      <c r="J6" s="2">
+        <v>7961.6635532905502</v>
+      </c>
+      <c r="K6" s="1">
+        <v>59680.8471760674</v>
+      </c>
+      <c r="L6" s="1">
         <v>3757.3592830689499</v>
       </c>
-      <c r="I6" s="1">
+      <c r="M6" s="1">
+        <v>69023.892206240998</v>
+      </c>
+      <c r="N6" s="1">
         <v>200.45055222268201</v>
       </c>
-      <c r="J6" s="1">
+      <c r="O6" s="1">
+        <v>333.19633078457201</v>
+      </c>
+      <c r="P6" s="1">
         <v>117181.94292290301</v>
       </c>
-      <c r="K6" s="1">
+      <c r="Q6" s="1">
         <v>74861.602089678301</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -736,28 +868,46 @@
         <v>5662.1815927131001</v>
       </c>
       <c r="E7" s="1">
+        <v>52994.4446439073</v>
+      </c>
+      <c r="F7" s="1">
         <v>797.95970821040396</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="1">
+        <v>5906.3262487826996</v>
+      </c>
+      <c r="H7" s="2">
         <v>5221.7732342678501</v>
       </c>
-      <c r="G7" s="1">
-        <v>94599.433891750406</v>
-      </c>
-      <c r="H7" s="1">
+      <c r="I7" s="1">
+        <v>227428.010475155</v>
+      </c>
+      <c r="J7" s="2">
+        <v>12951.9282524711</v>
+      </c>
+      <c r="K7" s="1">
+        <v>96363.541800367704</v>
+      </c>
+      <c r="L7" s="1">
         <v>4734.0420195553697</v>
       </c>
-      <c r="I7" s="1">
+      <c r="M7" s="1">
+        <v>94117.779983435204</v>
+      </c>
+      <c r="N7" s="1">
         <v>579.92204176205803</v>
       </c>
-      <c r="J7" s="1">
+      <c r="O7" s="1">
+        <v>2408.5009324350099</v>
+      </c>
+      <c r="P7" s="1">
         <v>124337.67221672799</v>
       </c>
-      <c r="K7" s="1">
+      <c r="Q7" s="1">
         <v>81381.066947812506</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -771,28 +921,46 @@
         <v>6467.0407539628004</v>
       </c>
       <c r="E8" s="1">
+        <v>64078.996420201001</v>
+      </c>
+      <c r="F8" s="1">
         <v>1231.72119404051</v>
       </c>
-      <c r="F8" s="2">
+      <c r="G8" s="1">
+        <v>8978.7202643320506</v>
+      </c>
+      <c r="H8" s="2">
         <v>8374.8103610041799</v>
       </c>
-      <c r="G8" s="1">
-        <v>101403.734074696</v>
-      </c>
-      <c r="H8" s="1">
+      <c r="I8" s="1">
+        <v>324666.54919871298</v>
+      </c>
+      <c r="J8" s="2">
+        <v>16665.1695787112</v>
+      </c>
+      <c r="K8" s="1">
+        <v>120912.102344923</v>
+      </c>
+      <c r="L8" s="1">
         <v>6858.1379876118799</v>
       </c>
-      <c r="I8" s="1">
+      <c r="M8" s="1">
+        <v>119521.270489674</v>
+      </c>
+      <c r="N8" s="1">
         <v>713.40720180574601</v>
       </c>
-      <c r="J8" s="1">
+      <c r="O8" s="1">
+        <v>5369.5711959608097</v>
+      </c>
+      <c r="P8" s="1">
         <v>124548.53842968799</v>
       </c>
-      <c r="K8" s="1">
+      <c r="Q8" s="1">
         <v>83143.184970693299</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -806,28 +974,46 @@
         <v>6677.6200249973599</v>
       </c>
       <c r="E9" s="1">
+        <v>72443.577076814894</v>
+      </c>
+      <c r="F9" s="1">
         <v>1727.60048485835</v>
       </c>
-      <c r="F9" s="2">
+      <c r="G9" s="1">
+        <v>12391.8141005003</v>
+      </c>
+      <c r="H9" s="2">
         <v>12430.148542774999</v>
       </c>
-      <c r="G9" s="1">
-        <v>105611.803169869</v>
-      </c>
-      <c r="H9" s="1">
+      <c r="I9" s="1">
+        <v>404452.89414167602</v>
+      </c>
+      <c r="J9" s="2">
+        <v>20170.623245663799</v>
+      </c>
+      <c r="K9" s="1">
+        <v>142831.70010932299</v>
+      </c>
+      <c r="L9" s="1">
         <v>10022.503228932601</v>
       </c>
-      <c r="I9" s="1">
+      <c r="M9" s="1">
+        <v>154387.24639883</v>
+      </c>
+      <c r="N9" s="1">
         <v>898.23776155674796</v>
       </c>
-      <c r="J9" s="1">
+      <c r="O9" s="1">
+        <v>8188.6122091153302</v>
+      </c>
+      <c r="P9" s="1">
         <v>121389.983337382</v>
       </c>
-      <c r="K9" s="1">
+      <c r="Q9" s="1">
         <v>82016.682079551902</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>6</v>
       </c>
@@ -841,28 +1027,46 @@
         <v>7493.3171621217898</v>
       </c>
       <c r="E10" s="1">
+        <v>86894.826595000995</v>
+      </c>
+      <c r="F10" s="1">
         <v>2362.3650670424399</v>
       </c>
-      <c r="F10" s="2">
+      <c r="G10" s="1">
+        <v>16621.114178426698</v>
+      </c>
+      <c r="H10" s="2">
         <v>20587.442224745701</v>
       </c>
-      <c r="G10" s="1">
-        <v>101256.038155812</v>
-      </c>
-      <c r="H10" s="1">
+      <c r="I10" s="1">
+        <v>511706.81531496602</v>
+      </c>
+      <c r="J10" s="2">
+        <v>24406.045720771199</v>
+      </c>
+      <c r="K10" s="1">
+        <v>169832.127972438</v>
+      </c>
+      <c r="L10" s="1">
         <v>10803.393482634399</v>
       </c>
-      <c r="I10" s="1">
+      <c r="M10" s="1">
+        <v>194737.015079754</v>
+      </c>
+      <c r="N10" s="1">
         <v>2072.6209123938602</v>
       </c>
-      <c r="J10" s="1">
+      <c r="O10" s="1">
+        <v>12857.675919258099</v>
+      </c>
+      <c r="P10" s="1">
         <v>117939.92514770701</v>
       </c>
-      <c r="K10" s="1">
+      <c r="Q10" s="1">
         <v>80054.931037718095</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>5</v>
       </c>
@@ -876,28 +1080,46 @@
         <v>8129.2998451592402</v>
       </c>
       <c r="E11" s="1">
+        <v>97991.801484433803</v>
+      </c>
+      <c r="F11" s="1">
         <v>3065.8244649973399</v>
       </c>
-      <c r="F11" s="2">
+      <c r="G11" s="1">
+        <v>21153.462454167398</v>
+      </c>
+      <c r="H11" s="2">
         <v>32657.341173983099</v>
       </c>
-      <c r="G11" s="1">
-        <v>91242.370890545499</v>
-      </c>
-      <c r="H11" s="1">
+      <c r="I11" s="1">
+        <v>709056.62044308498</v>
+      </c>
+      <c r="J11" s="2">
+        <v>28523.590763210501</v>
+      </c>
+      <c r="K11" s="1">
+        <v>191632.77253034801</v>
+      </c>
+      <c r="L11" s="1">
         <v>9873.4820198206107</v>
       </c>
-      <c r="I11" s="1">
+      <c r="M11" s="1">
+        <v>232715.07591540899</v>
+      </c>
+      <c r="N11" s="1">
         <v>5605.3712666789497</v>
       </c>
-      <c r="J11" s="1">
+      <c r="O11" s="1">
+        <v>26511.030959861699</v>
+      </c>
+      <c r="P11" s="1">
         <v>117025.30046122101</v>
       </c>
-      <c r="K11" s="1">
+      <c r="Q11" s="1">
         <v>80192.433778004197</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>4</v>
       </c>
@@ -911,28 +1133,46 @@
         <v>7197.55395485193</v>
       </c>
       <c r="E12" s="1">
+        <v>87556.830336833504</v>
+      </c>
+      <c r="F12" s="1">
         <v>3517.6104937896998</v>
       </c>
-      <c r="F12" s="2">
+      <c r="G12" s="1">
+        <v>23594.2871982078</v>
+      </c>
+      <c r="H12" s="2">
         <v>37338.508895075996</v>
       </c>
-      <c r="G12" s="1">
-        <v>70323.291408803503</v>
-      </c>
-      <c r="H12" s="1">
+      <c r="I12" s="1">
+        <v>739470.934469208</v>
+      </c>
+      <c r="J12" s="2">
+        <v>28543.278415793298</v>
+      </c>
+      <c r="K12" s="1">
+        <v>181052.37662838699</v>
+      </c>
+      <c r="L12" s="1">
         <v>5928.3316071394702</v>
       </c>
-      <c r="I12" s="1">
+      <c r="M12" s="1">
+        <v>216832.10902387099</v>
+      </c>
+      <c r="N12" s="1">
         <v>9543.1648218351602</v>
       </c>
-      <c r="J12" s="1">
+      <c r="O12" s="1">
+        <v>47971.573753192803</v>
+      </c>
+      <c r="P12" s="1">
         <v>96232.371325058106</v>
       </c>
-      <c r="K12" s="1">
+      <c r="Q12" s="1">
         <v>66571.8857277934</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>3</v>
       </c>
@@ -946,28 +1186,46 @@
         <v>4805.9454763048898</v>
       </c>
       <c r="E13" s="1">
+        <v>62277.426386598498</v>
+      </c>
+      <c r="F13" s="1">
         <v>3110.6583228335198</v>
       </c>
-      <c r="F13" s="2">
+      <c r="G13" s="1">
+        <v>19809.978444145901</v>
+      </c>
+      <c r="H13" s="2">
         <v>35467.572533225699</v>
       </c>
-      <c r="G13" s="1">
-        <v>45409.990592704802</v>
-      </c>
-      <c r="H13" s="1">
+      <c r="I13" s="1">
+        <v>651554.68736139196</v>
+      </c>
+      <c r="J13" s="2">
+        <v>22404.321558521398</v>
+      </c>
+      <c r="K13" s="1">
+        <v>132200.79864519899</v>
+      </c>
+      <c r="L13" s="1">
         <v>1758.9273243308801</v>
       </c>
-      <c r="I13" s="1">
+      <c r="M13" s="1">
+        <v>166340.62594863799</v>
+      </c>
+      <c r="N13" s="1">
         <v>12999.2391768621</v>
       </c>
-      <c r="J13" s="1">
+      <c r="O13" s="1">
+        <v>70068.066886725399</v>
+      </c>
+      <c r="P13" s="1">
         <v>71576.162778811806</v>
       </c>
-      <c r="K13" s="1">
+      <c r="Q13" s="1">
         <v>50329.169102781801</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>2</v>
       </c>
@@ -981,28 +1239,46 @@
         <v>4703.9879333736098</v>
       </c>
       <c r="E14" s="1">
+        <v>59724.711179073398</v>
+      </c>
+      <c r="F14" s="1">
         <v>3839.8657174885202</v>
       </c>
-      <c r="F14" s="2">
+      <c r="G14" s="1">
+        <v>21569.587475874199</v>
+      </c>
+      <c r="H14" s="2">
         <v>40843.165995684503</v>
       </c>
-      <c r="G14" s="1">
-        <v>40071.020130189499</v>
-      </c>
-      <c r="H14" s="1">
+      <c r="I14" s="1">
+        <v>699197.87517874094</v>
+      </c>
+      <c r="J14" s="2">
+        <v>24185.124632496401</v>
+      </c>
+      <c r="K14" s="1">
+        <v>123816.90938153199</v>
+      </c>
+      <c r="L14" s="1">
         <v>380.459165983319</v>
       </c>
-      <c r="I14" s="1">
+      <c r="M14" s="1">
+        <v>149833.288014914</v>
+      </c>
+      <c r="N14" s="1">
         <v>20835.983559038701</v>
       </c>
-      <c r="J14" s="1">
+      <c r="O14" s="1">
+        <v>113969.356148106</v>
+      </c>
+      <c r="P14" s="1">
         <v>65942.646528924204</v>
       </c>
-      <c r="K14" s="1">
+      <c r="Q14" s="1">
         <v>47623.047709947503</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>1</v>
       </c>
@@ -1016,28 +1292,46 @@
         <v>3964.1039772608001</v>
       </c>
       <c r="E15" s="1">
+        <v>46877.003328194303</v>
+      </c>
+      <c r="F15" s="1">
         <v>3741.5928706325499</v>
       </c>
-      <c r="F15" s="2">
+      <c r="G15" s="1">
+        <v>17173.0601798885</v>
+      </c>
+      <c r="H15" s="2">
         <v>39393.748689389802</v>
       </c>
-      <c r="G15" s="1">
-        <v>30087.313673168901</v>
-      </c>
-      <c r="H15" s="1">
+      <c r="I15" s="1">
+        <v>616190.60860153602</v>
+      </c>
+      <c r="J15" s="2">
+        <v>21182.020214055101</v>
+      </c>
+      <c r="K15" s="1">
+        <v>93220.871759840593</v>
+      </c>
+      <c r="L15" s="1">
         <v>167.01273980801099</v>
       </c>
-      <c r="I15" s="1">
+      <c r="M15" s="1">
+        <v>110362.662448073</v>
+      </c>
+      <c r="N15" s="1">
         <v>23167.833796081701</v>
       </c>
-      <c r="J15" s="1">
+      <c r="O15" s="1">
+        <v>135193.25717201899</v>
+      </c>
+      <c r="P15" s="1">
         <v>51323.210853908997</v>
       </c>
-      <c r="K15" s="1">
+      <c r="Q15" s="1">
         <v>37414.906158514903</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>14</v>
       </c>
@@ -1047,29 +1341,45 @@
       <c r="C16" t="s">
         <v>0</v>
       </c>
-      <c r="E16" s="1">
+      <c r="E16" s="1"/>
+      <c r="F16" s="1">
         <v>35.868559274026403</v>
       </c>
-      <c r="F16" s="2">
+      <c r="G16" s="1">
+        <v>280.89496543029401</v>
+      </c>
+      <c r="H16" s="2">
         <v>979.590678637667</v>
       </c>
-      <c r="G16" s="1">
-        <v>10547.1055404502</v>
-      </c>
-      <c r="H16" s="1">
+      <c r="I16" s="1">
+        <v>19745.956453112402</v>
+      </c>
+      <c r="J16" s="2">
+        <v>1050.18458681181</v>
+      </c>
+      <c r="K16" s="2">
+        <v>7939</v>
+      </c>
+      <c r="L16" s="1">
         <v>2773.2923883325602</v>
       </c>
-      <c r="I16" s="1">
-        <v>0</v>
-      </c>
-      <c r="J16" s="1">
+      <c r="M16" s="1">
+        <v>15420.3449608848</v>
+      </c>
+      <c r="N16" s="1">
+        <v>0</v>
+      </c>
+      <c r="O16" s="1">
+        <v>0</v>
+      </c>
+      <c r="P16" s="1">
         <v>63725.650599513603</v>
       </c>
-      <c r="K16" s="1">
+      <c r="Q16" s="1">
         <v>40009.3949797065</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>13</v>
       </c>
@@ -1079,29 +1389,45 @@
       <c r="C17" t="s">
         <v>0</v>
       </c>
-      <c r="E17" s="1">
+      <c r="E17" s="1"/>
+      <c r="F17" s="1">
         <v>61.204729369523598</v>
       </c>
-      <c r="F17" s="2">
+      <c r="G17" s="1">
+        <v>465.75193610409099</v>
+      </c>
+      <c r="H17" s="2">
         <v>1201.93972038215</v>
       </c>
-      <c r="G17" s="1">
-        <v>11796.8720129139</v>
-      </c>
-      <c r="H17" s="1">
+      <c r="I17" s="1">
+        <v>29518.535346385899</v>
+      </c>
+      <c r="J17" s="2">
+        <v>1733.96553221518</v>
+      </c>
+      <c r="K17" s="2">
+        <v>13269</v>
+      </c>
+      <c r="L17" s="1">
         <v>3374.0731419662402</v>
       </c>
-      <c r="I17" s="1">
-        <v>0</v>
-      </c>
-      <c r="J17" s="1">
+      <c r="M17" s="1">
+        <v>31488.826860063298</v>
+      </c>
+      <c r="N17" s="1">
+        <v>0</v>
+      </c>
+      <c r="O17" s="1">
+        <v>0</v>
+      </c>
+      <c r="P17" s="1">
         <v>61953.617402941702</v>
       </c>
-      <c r="K17" s="1">
+      <c r="Q17" s="1">
         <v>39267.500493782201</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>12</v>
       </c>
@@ -1111,29 +1437,45 @@
       <c r="C18" t="s">
         <v>0</v>
       </c>
-      <c r="E18" s="1">
+      <c r="E18" s="1"/>
+      <c r="F18" s="1">
         <v>166.91730541291901</v>
       </c>
-      <c r="F18" s="2">
+      <c r="G18" s="1">
+        <v>1278.6947275881801</v>
+      </c>
+      <c r="H18" s="2">
         <v>1854.4928007996</v>
       </c>
-      <c r="G18" s="1">
-        <v>15570.378567695199</v>
-      </c>
-      <c r="H18" s="1">
+      <c r="I18" s="1">
+        <v>49467.8982176442</v>
+      </c>
+      <c r="J18" s="2">
+        <v>2682.77664635275</v>
+      </c>
+      <c r="K18" s="2">
+        <v>19793</v>
+      </c>
+      <c r="L18" s="1">
         <v>4659.5681303445999</v>
       </c>
-      <c r="I18" s="1">
-        <v>0</v>
-      </c>
-      <c r="J18" s="1">
+      <c r="M18" s="1">
+        <v>53824.327960769901</v>
+      </c>
+      <c r="N18" s="1">
+        <v>0</v>
+      </c>
+      <c r="O18" s="1">
+        <v>0</v>
+      </c>
+      <c r="P18" s="1">
         <v>63951.726487806802</v>
       </c>
-      <c r="K18" s="1">
+      <c r="Q18" s="1">
         <v>40734.897141880298</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>11</v>
       </c>
@@ -1143,29 +1485,45 @@
       <c r="C19" t="s">
         <v>0</v>
       </c>
-      <c r="E19" s="1">
+      <c r="E19" s="1"/>
+      <c r="F19" s="1">
         <v>259.46955109795101</v>
       </c>
-      <c r="F19" s="2">
+      <c r="G19" s="1">
+        <v>1981.00225301772</v>
+      </c>
+      <c r="H19" s="2">
         <v>2911.6926748257501</v>
       </c>
-      <c r="G19" s="1">
-        <v>19831.435365161298</v>
-      </c>
-      <c r="H19" s="1">
+      <c r="I19" s="1">
+        <v>87196.136630802794</v>
+      </c>
+      <c r="J19" s="2">
+        <v>3701.0542912781202</v>
+      </c>
+      <c r="K19" s="2">
+        <v>24727</v>
+      </c>
+      <c r="L19" s="1">
         <v>6242.1614464206496</v>
       </c>
-      <c r="I19" s="1">
-        <v>0</v>
-      </c>
-      <c r="J19" s="1">
+      <c r="M19" s="1">
+        <v>83287.303557025603</v>
+      </c>
+      <c r="N19" s="1">
+        <v>0</v>
+      </c>
+      <c r="O19" s="1">
+        <v>0</v>
+      </c>
+      <c r="P19" s="1">
         <v>65499.398155419098</v>
       </c>
-      <c r="K19" s="1">
+      <c r="Q19" s="1">
         <v>42042.584455301498</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>10</v>
       </c>
@@ -1175,29 +1533,45 @@
       <c r="C20" t="s">
         <v>0</v>
       </c>
-      <c r="E20" s="1">
+      <c r="E20" s="1"/>
+      <c r="F20" s="1">
         <v>393.18848480685102</v>
       </c>
-      <c r="F20" s="2">
+      <c r="G20" s="1">
+        <v>2941.2613704556302</v>
+      </c>
+      <c r="H20" s="2">
         <v>5659.6219309011904</v>
       </c>
-      <c r="G20" s="1">
-        <v>25267.382254248801</v>
-      </c>
-      <c r="H20" s="1">
+      <c r="I20" s="1">
+        <v>167430.53064446501</v>
+      </c>
+      <c r="J20" s="2">
+        <v>5019.7181650545299</v>
+      </c>
+      <c r="K20" s="2">
+        <v>30345</v>
+      </c>
+      <c r="L20" s="1">
         <v>7473.8461896226499</v>
       </c>
-      <c r="I20" s="1">
+      <c r="M20" s="1">
+        <v>117903.930967796</v>
+      </c>
+      <c r="N20" s="1">
         <v>179.37030847911001</v>
       </c>
-      <c r="J20" s="1">
+      <c r="O20" s="1">
+        <v>298.29332152880198</v>
+      </c>
+      <c r="P20" s="1">
         <v>65091.9510618442</v>
       </c>
-      <c r="K20" s="1">
+      <c r="Q20" s="1">
         <v>42178.021680422098</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>9</v>
       </c>
@@ -1207,29 +1581,45 @@
       <c r="C21" t="s">
         <v>0</v>
       </c>
-      <c r="E21" s="1">
+      <c r="E21" s="1"/>
+      <c r="F21" s="1">
         <v>847.04448251226904</v>
       </c>
-      <c r="F21" s="2">
+      <c r="G21" s="1">
+        <v>6224.9633692777898</v>
+      </c>
+      <c r="H21" s="2">
         <v>9575.0456011774895</v>
       </c>
-      <c r="G21" s="1">
-        <v>36274.301361196303</v>
-      </c>
-      <c r="H21" s="1">
+      <c r="I21" s="1">
+        <v>281869.175113715</v>
+      </c>
+      <c r="J21" s="2">
+        <v>9247.3509243810295</v>
+      </c>
+      <c r="K21" s="2">
+        <v>52928</v>
+      </c>
+      <c r="L21" s="1">
         <v>8962.2641997762894</v>
       </c>
-      <c r="I21" s="1">
+      <c r="M21" s="1">
+        <v>166484.03495717299</v>
+      </c>
+      <c r="N21" s="1">
         <v>512.98459175131802</v>
       </c>
-      <c r="J21" s="1">
+      <c r="O21" s="1">
+        <v>2130.3498817066802</v>
+      </c>
+      <c r="P21" s="1">
         <v>67565.817499864803</v>
       </c>
-      <c r="K21" s="1">
+      <c r="Q21" s="1">
         <v>44342.9579671881</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>8</v>
       </c>
@@ -1239,29 +1629,45 @@
       <c r="C22" t="s">
         <v>0</v>
       </c>
-      <c r="E22" s="1">
+      <c r="E22" s="1"/>
+      <c r="F22" s="1">
         <v>1555.83509237306</v>
       </c>
-      <c r="F22" s="2">
+      <c r="G22" s="1">
+        <v>11071.9658511465</v>
+      </c>
+      <c r="H22" s="2">
         <v>15463.018047597399</v>
       </c>
-      <c r="G22" s="1">
-        <v>47480.353174948003</v>
-      </c>
-      <c r="H22" s="1">
+      <c r="I22" s="1">
+        <v>412947.21451953001</v>
+      </c>
+      <c r="J22" s="2">
+        <v>15248.4445755698</v>
+      </c>
+      <c r="K22" s="2">
+        <v>83391</v>
+      </c>
+      <c r="L22" s="1">
         <v>10952.9360535551</v>
       </c>
-      <c r="I22" s="1">
+      <c r="M22" s="1">
+        <v>208530.900470124</v>
+      </c>
+      <c r="N22" s="1">
         <v>608.76121231193997</v>
       </c>
-      <c r="J22" s="1">
+      <c r="O22" s="1">
+        <v>4543.6193434173802</v>
+      </c>
+      <c r="P22" s="1">
         <v>65314.3905427461</v>
       </c>
-      <c r="K22" s="1">
+      <c r="Q22" s="1">
         <v>43119.024335203401</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>7</v>
       </c>
@@ -1271,29 +1677,45 @@
       <c r="C23" t="s">
         <v>0</v>
       </c>
-      <c r="E23" s="1">
+      <c r="E23" s="1"/>
+      <c r="F23" s="1">
         <v>2352.3323735684398</v>
       </c>
-      <c r="F23" s="2">
+      <c r="G23" s="1">
+        <v>16267.781055548299</v>
+      </c>
+      <c r="H23" s="2">
         <v>22944.7611337993</v>
       </c>
-      <c r="G23" s="1">
-        <v>62358.169072636701</v>
-      </c>
-      <c r="H23" s="1">
+      <c r="I23" s="1">
+        <v>561665.75664040097</v>
+      </c>
+      <c r="J23" s="2">
+        <v>23945.8004612939</v>
+      </c>
+      <c r="K23" s="2">
+        <v>128744</v>
+      </c>
+      <c r="L23" s="1">
         <v>13488.6125537559</v>
       </c>
-      <c r="I23" s="1">
+      <c r="M23" s="1">
+        <v>252520.97208794701</v>
+      </c>
+      <c r="N23" s="1">
         <v>799.52407369711796</v>
       </c>
-      <c r="J23" s="1">
+      <c r="O23" s="1">
+        <v>6781.7449535577398</v>
+      </c>
+      <c r="P23" s="1">
         <v>61507.848943434699</v>
       </c>
-      <c r="K23" s="1">
+      <c r="Q23" s="1">
         <v>40989.765822723901</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>6</v>
       </c>
@@ -1303,29 +1725,45 @@
       <c r="C24" t="s">
         <v>0</v>
       </c>
-      <c r="E24" s="1">
+      <c r="E24" s="1"/>
+      <c r="F24" s="1">
         <v>3607.7303284606501</v>
       </c>
-      <c r="F24" s="2">
+      <c r="G24" s="1">
+        <v>24128.9408270155</v>
+      </c>
+      <c r="H24" s="2">
         <v>34012.705162054197</v>
       </c>
-      <c r="G24" s="1">
-        <v>76354.694622921394</v>
-      </c>
-      <c r="H24" s="1">
+      <c r="I24" s="1">
+        <v>719727.92669527605</v>
+      </c>
+      <c r="J24" s="2">
+        <v>35695.060961856499</v>
+      </c>
+      <c r="K24" s="2">
+        <v>194663</v>
+      </c>
+      <c r="L24" s="1">
         <v>12523.905111943001</v>
       </c>
-      <c r="I24" s="1">
+      <c r="M24" s="1">
+        <v>290012.21650918998</v>
+      </c>
+      <c r="N24" s="1">
         <v>1937.18755936714</v>
       </c>
-      <c r="J24" s="1">
+      <c r="O24" s="1">
+        <v>10866.0325262389</v>
+      </c>
+      <c r="P24" s="1">
         <v>57097.117568491303</v>
       </c>
-      <c r="K24" s="1">
+      <c r="Q24" s="1">
         <v>38169.336360151698</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>5</v>
       </c>
@@ -1335,29 +1773,45 @@
       <c r="C25" t="s">
         <v>0</v>
       </c>
-      <c r="E25" s="1">
+      <c r="E25" s="1"/>
+      <c r="F25" s="1">
         <v>4958.17627766639</v>
       </c>
-      <c r="F25" s="2">
+      <c r="G25" s="1">
+        <v>32372.7086878796</v>
+      </c>
+      <c r="H25" s="2">
         <v>49162.048989562601</v>
       </c>
-      <c r="G25" s="1">
-        <v>86867.783459435304</v>
-      </c>
-      <c r="H25" s="1">
+      <c r="I25" s="1">
+        <v>953384.56140229304</v>
+      </c>
+      <c r="J25" s="2">
+        <v>45544.271434501301</v>
+      </c>
+      <c r="K25" s="2">
+        <v>244344</v>
+      </c>
+      <c r="L25" s="1">
         <v>9641.3463135489092</v>
       </c>
-      <c r="I25" s="1">
+      <c r="M25" s="1">
+        <v>319169.01493874198</v>
+      </c>
+      <c r="N25" s="1">
         <v>4766.2133119480304</v>
       </c>
-      <c r="J25" s="1">
+      <c r="O25" s="1">
+        <v>22641.118320095899</v>
+      </c>
+      <c r="P25" s="1">
         <v>54760.295815320802</v>
       </c>
-      <c r="K25" s="1">
+      <c r="Q25" s="1">
         <v>36847.669776009199</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>4</v>
       </c>
@@ -1367,29 +1821,45 @@
       <c r="C26" t="s">
         <v>0</v>
       </c>
-      <c r="E26" s="1">
+      <c r="E26" s="1"/>
+      <c r="F26" s="1">
         <v>5556.5951131483698</v>
       </c>
-      <c r="F26" s="2">
+      <c r="G26" s="1">
+        <v>34928.245887316101</v>
+      </c>
+      <c r="H26" s="2">
         <v>48399.188138501297</v>
       </c>
-      <c r="G26" s="1">
-        <v>78052.987440609199</v>
-      </c>
-      <c r="H26" s="1">
+      <c r="I26" s="1">
+        <v>906839.83745009196</v>
+      </c>
+      <c r="J26" s="2">
+        <v>46498.811146259999</v>
+      </c>
+      <c r="K26" s="2">
+        <v>242195</v>
+      </c>
+      <c r="L26" s="1">
         <v>5121.7042037784004</v>
       </c>
-      <c r="I26" s="1">
+      <c r="M26" s="1">
+        <v>271974.19228910899</v>
+      </c>
+      <c r="N26" s="1">
         <v>7503.2825109897203</v>
       </c>
-      <c r="J26" s="1">
+      <c r="O26" s="1">
+        <v>38528.6087490637</v>
+      </c>
+      <c r="P26" s="1">
         <v>43206.315763751198</v>
       </c>
-      <c r="K26" s="1">
+      <c r="Q26" s="1">
         <v>29203.54883887</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>3</v>
       </c>
@@ -1399,29 +1869,45 @@
       <c r="C27" t="s">
         <v>0</v>
       </c>
-      <c r="E27" s="1">
+      <c r="E27" s="1"/>
+      <c r="F27" s="1">
         <v>4029.8665304145402</v>
       </c>
-      <c r="F27" s="2">
+      <c r="G27" s="1">
+        <v>23751.2640248514</v>
+      </c>
+      <c r="H27" s="2">
         <v>36791.664427351898</v>
       </c>
-      <c r="G27" s="1">
-        <v>51419.864913194702</v>
-      </c>
-      <c r="H27" s="1">
+      <c r="I27" s="1">
+        <v>685897.72565331496</v>
+      </c>
+      <c r="J27" s="2">
+        <v>33496.792099516701</v>
+      </c>
+      <c r="K27" s="2">
+        <v>163919</v>
+      </c>
+      <c r="L27" s="1">
         <v>1331.2874336208299</v>
       </c>
-      <c r="I27" s="1">
+      <c r="M27" s="1">
+        <v>185454.63515522701</v>
+      </c>
+      <c r="N27" s="1">
         <v>8917.9373916232998</v>
       </c>
-      <c r="J27" s="1">
+      <c r="O27" s="1">
+        <v>50429.134196497303</v>
+      </c>
+      <c r="P27" s="1">
         <v>29283.088765753499</v>
       </c>
-      <c r="K27" s="1">
+      <c r="Q27" s="1">
         <v>20022.905824427799</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>2</v>
       </c>
@@ -1431,29 +1917,45 @@
       <c r="C28" t="s">
         <v>0</v>
       </c>
-      <c r="E28" s="1">
+      <c r="E28" s="1"/>
+      <c r="F28" s="1">
         <v>3818.6111722422902</v>
       </c>
-      <c r="F28" s="2">
+      <c r="G28" s="1">
+        <v>19587.476145001499</v>
+      </c>
+      <c r="H28" s="2">
         <v>34848.668941745302</v>
       </c>
-      <c r="G28" s="1">
-        <v>40352.991684315602</v>
-      </c>
-      <c r="H28" s="1">
+      <c r="I28" s="1">
+        <v>590086.42538444104</v>
+      </c>
+      <c r="J28" s="2">
+        <v>28486.6502125714</v>
+      </c>
+      <c r="K28" s="2">
+        <v>116811</v>
+      </c>
+      <c r="L28" s="1">
         <v>193.27290625277899</v>
       </c>
-      <c r="I28" s="1">
+      <c r="M28" s="1">
+        <v>140683.882374298</v>
+      </c>
+      <c r="N28" s="1">
         <v>12279.956847609799</v>
       </c>
-      <c r="J28" s="1">
+      <c r="O28" s="1">
+        <v>68243.216705522398</v>
+      </c>
+      <c r="P28" s="1">
         <v>22967.3339007953</v>
       </c>
-      <c r="K28" s="1">
+      <c r="Q28" s="1">
         <v>16020.604332495999</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>1</v>
       </c>
@@ -1463,25 +1965,41 @@
       <c r="C29" t="s">
         <v>0</v>
       </c>
-      <c r="E29" s="1">
+      <c r="E29" s="1"/>
+      <c r="F29" s="1">
         <v>3123.0127465436599</v>
       </c>
-      <c r="F29" s="2">
+      <c r="G29" s="1">
+        <v>12968.349482752899</v>
+      </c>
+      <c r="H29" s="2">
         <v>27231.105850723201</v>
       </c>
-      <c r="G29" s="1">
-        <v>25958.0931464733</v>
-      </c>
-      <c r="H29" s="1">
+      <c r="I29" s="1">
+        <v>387002.93786506797</v>
+      </c>
+      <c r="J29" s="2">
+        <v>20103.870500991401</v>
+      </c>
+      <c r="K29" s="2">
+        <v>62758</v>
+      </c>
+      <c r="L29" s="1">
         <v>67.897980072262897</v>
       </c>
-      <c r="I29" s="1">
+      <c r="M29" s="1">
+        <v>81399.686374337805</v>
+      </c>
+      <c r="N29" s="1">
         <v>11516.040906820101</v>
       </c>
-      <c r="J29" s="1">
+      <c r="O29" s="1">
+        <v>64658.385992899501</v>
+      </c>
+      <c r="P29" s="1">
         <v>14170.4127573039</v>
       </c>
-      <c r="K29" s="1">
+      <c r="Q29" s="1">
         <v>9943.3943236052</v>
       </c>
     </row>
@@ -1492,20 +2010,25 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E002562B-DD6F-164B-BC33-738F7B5F11A1}">
-  <dimension ref="A1:K29"/>
+  <dimension ref="A1:Q29"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="4" max="4" width="11.5" customWidth="1"/>
-    <col min="5" max="5" width="12" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.83203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.5" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.5" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="11.5" customWidth="1"/>
+    <col min="6" max="6" width="12" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.83203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.83203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16.83203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.5" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.5" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>23</v>
       </c>
@@ -1519,28 +2042,46 @@
         <v>25</v>
       </c>
       <c r="E1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" t="s">
         <v>26</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H1" t="s">
         <v>19</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
+        <v>29</v>
+      </c>
+      <c r="J1" t="s">
         <v>17</v>
       </c>
-      <c r="H1" t="s">
+      <c r="K1" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1" t="s">
         <v>18</v>
       </c>
-      <c r="I1" t="s">
+      <c r="M1" t="s">
+        <v>31</v>
+      </c>
+      <c r="N1" t="s">
         <v>20</v>
       </c>
-      <c r="J1" t="s">
+      <c r="O1" t="s">
+        <v>32</v>
+      </c>
+      <c r="P1" t="s">
         <v>16</v>
       </c>
-      <c r="K1" t="s">
+      <c r="Q1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -1553,29 +2094,47 @@
       <c r="D2" s="1">
         <v>36.159928838606099</v>
       </c>
-      <c r="E2" s="1">
+      <c r="E2" s="2">
+        <v>319</v>
+      </c>
+      <c r="F2" s="1">
         <v>22.034416734194401</v>
       </c>
-      <c r="F2" s="1">
+      <c r="G2" s="2">
+        <v>168</v>
+      </c>
+      <c r="H2" s="1">
         <v>355.32041082233798</v>
       </c>
-      <c r="G2" s="1">
-        <v>20535.585789194702</v>
-      </c>
-      <c r="H2" s="1">
+      <c r="I2" s="1">
+        <v>16179.1522058399</v>
+      </c>
+      <c r="J2" s="2">
+        <v>565.91646239513</v>
+      </c>
+      <c r="K2" s="1">
+        <v>3684.8804839214499</v>
+      </c>
+      <c r="L2" s="1">
         <v>1205.6450211404399</v>
       </c>
-      <c r="I2" s="1">
-        <v>0</v>
-      </c>
-      <c r="J2" s="1">
+      <c r="M2" s="2">
+        <v>7041</v>
+      </c>
+      <c r="N2" s="1">
+        <v>0</v>
+      </c>
+      <c r="O2" s="1">
+        <v>0</v>
+      </c>
+      <c r="P2" s="1">
         <v>90350.229755512599</v>
       </c>
-      <c r="K2" s="1">
+      <c r="Q2" s="1">
         <v>55198.5750668447</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -1588,29 +2147,47 @@
       <c r="D3" s="1">
         <v>210.334715759067</v>
       </c>
-      <c r="E3" s="1">
+      <c r="E3" s="2">
+        <v>1837</v>
+      </c>
+      <c r="F3" s="1">
         <v>39.4145865474269</v>
       </c>
-      <c r="F3" s="1">
+      <c r="G3" s="2">
+        <v>293</v>
+      </c>
+      <c r="H3" s="1">
         <v>471.21227118233702</v>
       </c>
-      <c r="G3" s="1">
-        <v>24199.264253060501</v>
-      </c>
-      <c r="H3" s="1">
+      <c r="I3" s="1">
+        <v>23925.143765336001</v>
+      </c>
+      <c r="J3" s="2">
+        <v>1099.55333023096</v>
+      </c>
+      <c r="K3" s="1">
+        <v>7608.2674992268103</v>
+      </c>
+      <c r="L3" s="1">
         <v>1478.0992456675899</v>
       </c>
-      <c r="I3">
-        <v>0</v>
-      </c>
-      <c r="J3" s="1">
+      <c r="M3" s="2">
+        <v>16923</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3" s="1">
+        <v>0</v>
+      </c>
+      <c r="P3" s="1">
         <v>92001.466114394294</v>
       </c>
-      <c r="K3" s="1">
+      <c r="Q3" s="1">
         <v>56309.240982367999</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -1623,29 +2200,47 @@
       <c r="D4" s="1">
         <v>755.17097657026795</v>
       </c>
-      <c r="E4" s="1">
+      <c r="E4" s="2">
+        <v>6689</v>
+      </c>
+      <c r="F4" s="1">
         <v>94.610650709218106</v>
       </c>
-      <c r="F4" s="1">
+      <c r="G4" s="2">
+        <v>725</v>
+      </c>
+      <c r="H4" s="1">
         <v>748.97853731957196</v>
       </c>
-      <c r="G4" s="1">
-        <v>35949.191362364101</v>
-      </c>
-      <c r="H4" s="1">
+      <c r="I4" s="1">
+        <v>35954.9775775702</v>
+      </c>
+      <c r="J4" s="2">
+        <v>2350.78257535998</v>
+      </c>
+      <c r="K4" s="1">
+        <v>16763.800520517601</v>
+      </c>
+      <c r="L4" s="1">
         <v>1732.37581959659</v>
       </c>
-      <c r="I4">
-        <v>0</v>
-      </c>
-      <c r="J4" s="1">
+      <c r="M4" s="2">
+        <v>29293</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4" s="1">
+        <v>0</v>
+      </c>
+      <c r="P4" s="1">
         <v>95845.041376111796</v>
       </c>
-      <c r="K4" s="1">
+      <c r="Q4" s="1">
         <v>57536.610010473501</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>11</v>
       </c>
@@ -1658,29 +2253,47 @@
       <c r="D5" s="1">
         <v>1575.42903839835</v>
       </c>
-      <c r="E5" s="1">
+      <c r="E5" s="2">
+        <v>14231</v>
+      </c>
+      <c r="F5" s="1">
         <v>179.65668246493399</v>
       </c>
-      <c r="F5" s="1">
+      <c r="G5" s="2">
+        <v>1368</v>
+      </c>
+      <c r="H5" s="1">
         <v>1078.3247042913699</v>
       </c>
-      <c r="G5" s="1">
-        <v>41385.655568557602</v>
-      </c>
-      <c r="H5" s="1">
+      <c r="I5" s="1">
+        <v>47398.881713042501</v>
+      </c>
+      <c r="J5" s="2">
+        <v>4186.4664226448003</v>
+      </c>
+      <c r="K5" s="1">
+        <v>29461.881794085701</v>
+      </c>
+      <c r="L5" s="1">
         <v>2051.42488497255</v>
       </c>
-      <c r="I5">
-        <v>0</v>
-      </c>
-      <c r="J5" s="1">
+      <c r="M5" s="2">
+        <v>43246</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5" s="1">
+        <v>0</v>
+      </c>
+      <c r="P5" s="1">
         <v>98117.404711791707</v>
       </c>
-      <c r="K5" s="1">
+      <c r="Q5" s="1">
         <v>62314.640167808597</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -1693,29 +2306,47 @@
       <c r="D6" s="1">
         <v>3122.8871557037101</v>
       </c>
-      <c r="E6" s="1">
+      <c r="E6" s="2">
+        <v>28634</v>
+      </c>
+      <c r="F6" s="1">
         <v>322.87235296295802</v>
       </c>
-      <c r="F6" s="1">
+      <c r="G6" s="2">
+        <v>2367</v>
+      </c>
+      <c r="H6" s="1">
         <v>2558.73855992571</v>
       </c>
-      <c r="G6" s="1">
-        <v>51594.448092163497</v>
-      </c>
-      <c r="H6" s="1">
+      <c r="I6" s="1">
+        <v>80723.008526516103</v>
+      </c>
+      <c r="J6" s="2">
+        <v>6862.1727026288399</v>
+      </c>
+      <c r="K6" s="1">
+        <v>49072.424028472502</v>
+      </c>
+      <c r="L6" s="1">
         <v>2638.4901581972799</v>
       </c>
-      <c r="I6" s="1">
+      <c r="M6" s="2">
+        <v>57610</v>
+      </c>
+      <c r="N6" s="1">
         <v>87.738182751532193</v>
       </c>
-      <c r="J6" s="1">
+      <c r="O6" s="1">
+        <v>144.85129265953299</v>
+      </c>
+      <c r="P6" s="1">
         <v>97210.410166385205</v>
       </c>
-      <c r="K6" s="1">
+      <c r="Q6" s="1">
         <v>62045.2456145748</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -1728,29 +2359,47 @@
       <c r="D7" s="1">
         <v>4886.5307136194897</v>
       </c>
-      <c r="E7" s="1">
+      <c r="E7" s="2">
+        <v>46899</v>
+      </c>
+      <c r="F7" s="1">
         <v>659.51659506351803</v>
       </c>
-      <c r="F7" s="1">
+      <c r="G7" s="2">
+        <v>4894</v>
+      </c>
+      <c r="H7" s="1">
         <v>3991.41740699092</v>
       </c>
-      <c r="G7" s="1">
-        <v>60490.861182656197</v>
-      </c>
-      <c r="H7" s="1">
+      <c r="I7" s="1">
+        <v>153775.29268987</v>
+      </c>
+      <c r="J7" s="2">
+        <v>11269.4510452011</v>
+      </c>
+      <c r="K7" s="1">
+        <v>79570.491876144704</v>
+      </c>
+      <c r="L7" s="1">
         <v>3369.5524972613398</v>
       </c>
-      <c r="I7" s="1">
+      <c r="M7" s="2">
+        <v>78729</v>
+      </c>
+      <c r="N7" s="1">
         <v>346.44176318324702</v>
       </c>
-      <c r="J7" s="1">
+      <c r="O7" s="1">
+        <v>1387.0659354223501</v>
+      </c>
+      <c r="P7" s="1">
         <v>102926.86246957201</v>
       </c>
-      <c r="K7" s="1">
+      <c r="Q7" s="1">
         <v>69846.065165256805</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -1763,29 +2412,47 @@
       <c r="D8" s="1">
         <v>5570.27773992108</v>
       </c>
-      <c r="E8" s="1">
+      <c r="E8" s="2">
+        <v>56377</v>
+      </c>
+      <c r="F8" s="1">
         <v>1048.8323760717601</v>
       </c>
-      <c r="F8" s="1">
+      <c r="G8" s="2">
+        <v>7421</v>
+      </c>
+      <c r="H8" s="1">
         <v>6795.5266068207902</v>
       </c>
-      <c r="G8" s="1">
-        <v>68821.315490219204</v>
-      </c>
-      <c r="H8" s="1">
+      <c r="I8" s="1">
+        <v>229366.82233089299</v>
+      </c>
+      <c r="J8" s="2">
+        <v>14725.2997071187</v>
+      </c>
+      <c r="K8" s="1">
+        <v>103894.364874013</v>
+      </c>
+      <c r="L8" s="1">
         <v>5038.9446489478796</v>
       </c>
-      <c r="I8" s="1">
+      <c r="M8" s="2">
+        <v>101093</v>
+      </c>
+      <c r="N8" s="1">
         <v>415.41063117379298</v>
       </c>
-      <c r="J8" s="1">
+      <c r="O8" s="1">
+        <v>3621.0665002127198</v>
+      </c>
+      <c r="P8" s="1">
         <v>106206.729450813</v>
       </c>
-      <c r="K8" s="1">
+      <c r="Q8" s="1">
         <v>70709.505373722495</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -1798,29 +2465,47 @@
       <c r="D9" s="1">
         <v>5840.7350319144998</v>
       </c>
-      <c r="E9" s="1">
+      <c r="E9" s="2">
+        <v>64896</v>
+      </c>
+      <c r="F9" s="1">
         <v>1484.6138884368199</v>
       </c>
-      <c r="F9" s="1">
+      <c r="G9" s="2">
+        <v>10578</v>
+      </c>
+      <c r="H9" s="1">
         <v>9220.5814719521404</v>
       </c>
-      <c r="G9" s="1">
-        <v>75619.978243938502</v>
-      </c>
-      <c r="H9" s="1">
+      <c r="I9" s="1">
+        <v>304405.56778870901</v>
+      </c>
+      <c r="J9" s="2">
+        <v>17823.6004731795</v>
+      </c>
+      <c r="K9" s="1">
+        <v>122465.941834668</v>
+      </c>
+      <c r="L9" s="1">
         <v>7447.6092126076101</v>
       </c>
-      <c r="I9" s="1">
+      <c r="M9" s="2">
+        <v>134701</v>
+      </c>
+      <c r="N9" s="1">
         <v>494.44171836475698</v>
       </c>
-      <c r="J9" s="1">
+      <c r="O9" s="1">
+        <v>6061.7853453822399</v>
+      </c>
+      <c r="P9" s="1">
         <v>103239.166063706</v>
       </c>
-      <c r="K9" s="1">
+      <c r="Q9" s="1">
         <v>71121.424648442699</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>6</v>
       </c>
@@ -1833,29 +2518,47 @@
       <c r="D10" s="1">
         <v>6505.9976170607397</v>
       </c>
-      <c r="E10" s="1">
+      <c r="E10" s="2">
+        <v>78826</v>
+      </c>
+      <c r="F10" s="1">
         <v>2044.4521076507499</v>
       </c>
-      <c r="F10" s="1">
+      <c r="G10" s="2">
+        <v>14460</v>
+      </c>
+      <c r="H10" s="1">
         <v>16306.6233185903</v>
       </c>
-      <c r="G10" s="1">
-        <v>70603.651477848602</v>
-      </c>
-      <c r="H10" s="1">
+      <c r="I10" s="1">
+        <v>419172.404648308</v>
+      </c>
+      <c r="J10" s="2">
+        <v>21664.3349913368</v>
+      </c>
+      <c r="K10" s="1">
+        <v>146840.32300008801</v>
+      </c>
+      <c r="L10" s="1">
         <v>8939.7834843230594</v>
       </c>
-      <c r="I10" s="1">
+      <c r="M10" s="2">
+        <v>168645</v>
+      </c>
+      <c r="N10" s="1">
         <v>1322.1845081261999</v>
       </c>
-      <c r="J10" s="1">
+      <c r="O10" s="1">
+        <v>9863.4263919837304</v>
+      </c>
+      <c r="P10" s="1">
         <v>100430.495382101</v>
       </c>
-      <c r="K10" s="1">
+      <c r="Q10" s="1">
         <v>69780.673663897003</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>5</v>
       </c>
@@ -1868,29 +2571,47 @@
       <c r="D11" s="1">
         <v>6953.25625312998</v>
       </c>
-      <c r="E11" s="1">
+      <c r="E11" s="2">
+        <v>88034</v>
+      </c>
+      <c r="F11" s="1">
         <v>2622.3094113862699</v>
       </c>
-      <c r="F11" s="1">
+      <c r="G11" s="2">
+        <v>18137</v>
+      </c>
+      <c r="H11" s="1">
         <v>25666.444183610602</v>
       </c>
-      <c r="G11" s="1">
-        <v>66406.970486713195</v>
-      </c>
-      <c r="H11" s="1">
+      <c r="I11" s="1">
+        <v>581426.26581202098</v>
+      </c>
+      <c r="J11" s="2">
+        <v>25061.829421027502</v>
+      </c>
+      <c r="K11" s="1">
+        <v>165013.01060465799</v>
+      </c>
+      <c r="L11" s="1">
         <v>7599.00745516807</v>
       </c>
-      <c r="I11" s="1">
+      <c r="M11" s="2">
+        <v>206497</v>
+      </c>
+      <c r="N11" s="1">
         <v>4166.9852968654104</v>
       </c>
-      <c r="J11" s="1">
+      <c r="O11" s="1">
+        <v>20781.361563621798</v>
+      </c>
+      <c r="P11" s="1">
         <v>97810.253968283403</v>
       </c>
-      <c r="K11" s="1">
+      <c r="Q11" s="1">
         <v>70084.460442772601</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>4</v>
       </c>
@@ -1903,29 +2624,47 @@
       <c r="D12" s="1">
         <v>6133.6922469671199</v>
       </c>
-      <c r="E12" s="1">
+      <c r="E12" s="2">
+        <v>77970</v>
+      </c>
+      <c r="F12" s="1">
         <v>2967.8893359683698</v>
       </c>
-      <c r="F12" s="1">
+      <c r="G12" s="2">
+        <v>19700</v>
+      </c>
+      <c r="H12" s="1">
         <v>31068.190418001301</v>
       </c>
-      <c r="G12" s="1">
-        <v>50955.3786378765</v>
-      </c>
-      <c r="H12" s="1">
+      <c r="I12" s="1">
+        <v>627902.59894099098</v>
+      </c>
+      <c r="J12" s="2">
+        <v>24668.035352211398</v>
+      </c>
+      <c r="K12" s="1">
+        <v>154152.59280655801</v>
+      </c>
+      <c r="L12" s="1">
         <v>3877.4105117599802</v>
       </c>
-      <c r="I12" s="1">
+      <c r="M12" s="2">
+        <v>195785</v>
+      </c>
+      <c r="N12" s="1">
         <v>7121.4898909630801</v>
       </c>
-      <c r="J12" s="1">
+      <c r="O12" s="1">
+        <v>38105.3621383356</v>
+      </c>
+      <c r="P12" s="1">
         <v>80994.201656676494</v>
       </c>
-      <c r="K12" s="1">
+      <c r="Q12" s="1">
         <v>57142.800067876698</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>3</v>
       </c>
@@ -1938,29 +2677,47 @@
       <c r="D13" s="1">
         <v>3924.1454093416501</v>
       </c>
-      <c r="E13" s="1">
+      <c r="E13" s="2">
+        <v>54775</v>
+      </c>
+      <c r="F13" s="1">
         <v>2530.46882220013</v>
       </c>
-      <c r="F13" s="1">
+      <c r="G13" s="2">
+        <v>16050</v>
+      </c>
+      <c r="H13" s="1">
         <v>28562.254090623501</v>
       </c>
-      <c r="G13" s="1">
-        <v>36209.117019673598</v>
-      </c>
-      <c r="H13" s="1">
+      <c r="I13" s="1">
+        <v>573794.913110152</v>
+      </c>
+      <c r="J13" s="2">
+        <v>18954.8736874364</v>
+      </c>
+      <c r="K13" s="1">
+        <v>111113.749800847</v>
+      </c>
+      <c r="L13" s="1">
         <v>1267.62332415935</v>
       </c>
-      <c r="I13" s="1">
+      <c r="M13" s="2">
+        <v>149786</v>
+      </c>
+      <c r="N13" s="1">
         <v>9753.0242400838306</v>
       </c>
-      <c r="J13" s="1">
+      <c r="O13" s="1">
+        <v>57590.394824632996</v>
+      </c>
+      <c r="P13" s="1">
         <v>59077.403328476401</v>
       </c>
-      <c r="K13" s="1">
+      <c r="Q13" s="1">
         <v>43155.481129965301</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>2</v>
       </c>
@@ -1973,29 +2730,47 @@
       <c r="D14" s="1">
         <v>3561.5253558592899</v>
       </c>
-      <c r="E14" s="1">
+      <c r="E14" s="2">
+        <v>51284</v>
+      </c>
+      <c r="F14" s="1">
         <v>2845.5314587020498</v>
       </c>
-      <c r="F14" s="1">
+      <c r="G14" s="2">
+        <v>16198</v>
+      </c>
+      <c r="H14" s="1">
         <v>33611.392735452697</v>
       </c>
-      <c r="G14" s="1">
-        <v>31401.300423482498</v>
-      </c>
-      <c r="H14" s="1">
+      <c r="I14" s="1">
+        <v>629878.30356330902</v>
+      </c>
+      <c r="J14" s="2">
+        <v>19255.274998880501</v>
+      </c>
+      <c r="K14" s="1">
+        <v>98164.978810965695</v>
+      </c>
+      <c r="L14" s="1">
         <v>217.89948573456999</v>
       </c>
-      <c r="I14" s="1">
+      <c r="M14" s="2">
+        <v>134657</v>
+      </c>
+      <c r="N14" s="1">
         <v>15989.268430030899</v>
       </c>
-      <c r="J14" s="1">
+      <c r="O14" s="1">
+        <v>94044.2904778628</v>
+      </c>
+      <c r="P14" s="1">
         <v>54816.379798116403</v>
       </c>
-      <c r="K14" s="1">
+      <c r="Q14" s="1">
         <v>40189.834988506198</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>1</v>
       </c>
@@ -2008,29 +2783,47 @@
       <c r="D15" s="1">
         <v>2872.4362132907399</v>
       </c>
-      <c r="E15" s="1">
+      <c r="E15" s="2">
+        <v>40054</v>
+      </c>
+      <c r="F15" s="1">
         <v>2674.4782517745698</v>
       </c>
-      <c r="F15" s="1">
+      <c r="G15" s="2">
+        <v>12568</v>
+      </c>
+      <c r="H15" s="1">
         <v>31783.288336023099</v>
       </c>
-      <c r="G15" s="1">
-        <v>23661.447827027299</v>
-      </c>
-      <c r="H15" s="1">
+      <c r="I15" s="1">
+        <v>565466.74441058002</v>
+      </c>
+      <c r="J15" s="2">
+        <v>16322.042465442701</v>
+      </c>
+      <c r="K15" s="1">
+        <v>73713.348484328599</v>
+      </c>
+      <c r="L15" s="1">
         <v>102.968938857062</v>
       </c>
-      <c r="I15" s="1">
+      <c r="M15" s="2">
+        <v>98668</v>
+      </c>
+      <c r="N15" s="1">
         <v>18356.632086485599</v>
       </c>
-      <c r="J15" s="1">
+      <c r="O15" s="1">
+        <v>113345.89235853701</v>
+      </c>
+      <c r="P15" s="1">
         <v>44040.047577108096</v>
       </c>
-      <c r="K15" s="1">
+      <c r="Q15" s="1">
         <v>30742.587748637801</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>14</v>
       </c>
@@ -2040,29 +2833,44 @@
       <c r="C16" t="s">
         <v>0</v>
       </c>
-      <c r="E16" s="1">
+      <c r="F16" s="1">
         <v>26.6301551391632</v>
       </c>
-      <c r="F16" s="1">
+      <c r="G16" s="1">
+        <v>205.27612717325701</v>
+      </c>
+      <c r="H16" s="1">
         <v>732.17669793488994</v>
       </c>
-      <c r="G16" s="1">
-        <v>6903.3856171284597</v>
-      </c>
-      <c r="H16" s="1">
+      <c r="I16" s="1">
+        <v>15088.929206086001</v>
+      </c>
+      <c r="J16" s="2">
+        <v>1050.18458681181</v>
+      </c>
+      <c r="K16" s="1">
+        <v>5640.2167381959898</v>
+      </c>
+      <c r="L16" s="1">
         <v>1882.3261356478499</v>
       </c>
-      <c r="I16">
-        <v>0</v>
-      </c>
-      <c r="J16" s="1">
+      <c r="M16" s="1">
+        <v>10757.608567495099</v>
+      </c>
+      <c r="N16">
+        <v>0</v>
+      </c>
+      <c r="O16" s="1">
+        <v>0</v>
+      </c>
+      <c r="P16" s="1">
         <v>52459.133047528499</v>
       </c>
-      <c r="K16" s="1">
+      <c r="Q16" s="1">
         <v>32341.602525145499</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>13</v>
       </c>
@@ -2072,29 +2880,44 @@
       <c r="C17" t="s">
         <v>0</v>
       </c>
-      <c r="E17" s="1">
+      <c r="F17" s="1">
         <v>48.451951991482403</v>
       </c>
-      <c r="F17" s="1">
+      <c r="G17" s="1">
+        <v>363.68992382362302</v>
+      </c>
+      <c r="H17" s="1">
         <v>875.66547185091201</v>
       </c>
-      <c r="G17" s="1">
-        <v>7572.9497652494201</v>
-      </c>
-      <c r="H17" s="1">
+      <c r="I17" s="1">
+        <v>22583.316354668499</v>
+      </c>
+      <c r="J17" s="2">
+        <v>1733.96553221518</v>
+      </c>
+      <c r="K17" s="1">
+        <v>9481.4873526639403</v>
+      </c>
+      <c r="L17" s="1">
         <v>2063.3176114873099</v>
       </c>
-      <c r="I17">
-        <v>0</v>
-      </c>
-      <c r="J17" s="1">
+      <c r="M17" s="1">
+        <v>24313.984307127001</v>
+      </c>
+      <c r="N17">
+        <v>0</v>
+      </c>
+      <c r="O17" s="1">
+        <v>0</v>
+      </c>
+      <c r="P17" s="1">
         <v>51487.6114650327</v>
       </c>
-      <c r="K17" s="1">
+      <c r="Q17" s="1">
         <v>31226.703848296798</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>12</v>
       </c>
@@ -2104,29 +2927,44 @@
       <c r="C18" t="s">
         <v>0</v>
       </c>
-      <c r="E18" s="1">
+      <c r="F18" s="1">
         <v>135.01172415997999</v>
       </c>
-      <c r="F18" s="1">
+      <c r="G18" s="1">
+        <v>1021.34157824204</v>
+      </c>
+      <c r="H18" s="1">
         <v>1522.39056592836</v>
       </c>
-      <c r="G18" s="1">
-        <v>10728.119445366399</v>
-      </c>
-      <c r="H18" s="1">
+      <c r="I18" s="1">
+        <v>36610.526736764397</v>
+      </c>
+      <c r="J18" s="2">
+        <v>2682.77664635275</v>
+      </c>
+      <c r="K18" s="1">
+        <v>14188.432687033999</v>
+      </c>
+      <c r="L18" s="1">
         <v>3182.9730794914199</v>
       </c>
-      <c r="I18">
-        <v>0</v>
-      </c>
-      <c r="J18" s="1">
+      <c r="M18" s="1">
+        <v>41506.211055813001</v>
+      </c>
+      <c r="N18">
+        <v>0</v>
+      </c>
+      <c r="O18" s="1">
+        <v>0</v>
+      </c>
+      <c r="P18" s="1">
         <v>53001.885335280604</v>
       </c>
-      <c r="K18" s="1">
+      <c r="Q18" s="1">
         <v>31788.756570498401</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>11</v>
       </c>
@@ -2136,29 +2974,44 @@
       <c r="C19" t="s">
         <v>0</v>
       </c>
-      <c r="E19" s="1">
+      <c r="F19" s="1">
         <v>217.241820689961</v>
       </c>
-      <c r="F19" s="1">
+      <c r="G19" s="1">
+        <v>1591.7744885314901</v>
+      </c>
+      <c r="H19" s="1">
         <v>2386.2039972033499</v>
       </c>
-      <c r="G19" s="1">
-        <v>13516.419112613899</v>
-      </c>
-      <c r="H19" s="1">
+      <c r="I19" s="1">
+        <v>62963.494744445001</v>
+      </c>
+      <c r="J19" s="2">
+        <v>3701.0542912781202</v>
+      </c>
+      <c r="K19" s="1">
+        <v>17701.336188889501</v>
+      </c>
+      <c r="L19" s="1">
         <v>4173.4852622846001</v>
       </c>
-      <c r="I19">
-        <v>0</v>
-      </c>
-      <c r="J19" s="1">
+      <c r="M19" s="1">
+        <v>67837.328268647005</v>
+      </c>
+      <c r="N19">
+        <v>0</v>
+      </c>
+      <c r="O19" s="1">
+        <v>0</v>
+      </c>
+      <c r="P19" s="1">
         <v>54004.563539681803</v>
       </c>
-      <c r="K19" s="1">
+      <c r="Q19" s="1">
         <v>34295.186404271903</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>10</v>
       </c>
@@ -2168,29 +3021,44 @@
       <c r="C20" t="s">
         <v>0</v>
       </c>
-      <c r="E20" s="1">
+      <c r="F20" s="1">
         <v>335.29732433341002</v>
       </c>
-      <c r="F20" s="1">
+      <c r="G20" s="1">
+        <v>2411.2380659691098</v>
+      </c>
+      <c r="H20" s="1">
         <v>4904.3715053904198</v>
       </c>
-      <c r="G20" s="1">
-        <v>18243.6701981068</v>
-      </c>
-      <c r="H20" s="1">
+      <c r="I20" s="1">
+        <v>118718.817238334</v>
+      </c>
+      <c r="J20" s="2">
+        <v>5019.7181650545299</v>
+      </c>
+      <c r="K20" s="1">
+        <v>22143.206943608599</v>
+      </c>
+      <c r="L20" s="1">
         <v>5418.7089590147798</v>
       </c>
-      <c r="I20" s="1">
+      <c r="M20" s="1">
+        <v>97371.730031432206</v>
+      </c>
+      <c r="N20" s="1">
         <v>73.9401451264157</v>
       </c>
-      <c r="J20" s="1">
+      <c r="O20" s="1">
+        <v>122.258142057168</v>
+      </c>
+      <c r="P20" s="1">
         <v>53494.462588376002</v>
       </c>
-      <c r="K20" s="1">
+      <c r="Q20" s="1">
         <v>33905.283822597601</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>9</v>
       </c>
@@ -2200,29 +3068,44 @@
       <c r="C21" t="s">
         <v>0</v>
       </c>
-      <c r="E21" s="1">
+      <c r="F21" s="1">
         <v>714.973494068067</v>
       </c>
-      <c r="F21" s="1">
+      <c r="G21" s="1">
+        <v>5159.2581275157299</v>
+      </c>
+      <c r="H21" s="1">
         <v>7890.9428204744399</v>
       </c>
-      <c r="G21" s="1">
-        <v>24637.452332464902</v>
-      </c>
-      <c r="H21" s="1">
+      <c r="I21" s="1">
+        <v>216950.69611149401</v>
+      </c>
+      <c r="J21" s="2">
+        <v>9247.3509243810295</v>
+      </c>
+      <c r="K21" s="1">
+        <v>39870.306614774701</v>
+      </c>
+      <c r="L21" s="1">
         <v>6607.8055836112298</v>
       </c>
-      <c r="I21" s="1">
+      <c r="M21" s="1">
+        <v>140591.48595780099</v>
+      </c>
+      <c r="N21" s="1">
         <v>319.383499940842</v>
       </c>
-      <c r="J21" s="1">
+      <c r="O21" s="1">
+        <v>1245.1815352747799</v>
+      </c>
+      <c r="P21" s="1">
         <v>55783.629033686098</v>
       </c>
-      <c r="K21" s="1">
+      <c r="Q21" s="1">
         <v>37632.573317415503</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>8</v>
       </c>
@@ -2232,29 +3115,44 @@
       <c r="C22" t="s">
         <v>0</v>
       </c>
-      <c r="E22" s="1">
+      <c r="F22" s="1">
         <v>1335.2326714440201</v>
       </c>
-      <c r="F22" s="1">
+      <c r="G22" s="1">
+        <v>9300.8932037122504</v>
+      </c>
+      <c r="H22" s="1">
         <v>13193.520078261499</v>
       </c>
-      <c r="G22" s="1">
-        <v>35868.234387963697</v>
-      </c>
-      <c r="H22" s="1">
+      <c r="I22" s="1">
+        <v>332349.238916095</v>
+      </c>
+      <c r="J22" s="2">
+        <v>15248.4445755698</v>
+      </c>
+      <c r="K22" s="1">
+        <v>66134.925221953104</v>
+      </c>
+      <c r="L22" s="1">
         <v>8590.7714098890792</v>
       </c>
-      <c r="I22" s="1">
+      <c r="M22" s="1">
+        <v>177917.05136431701</v>
+      </c>
+      <c r="N22" s="1">
         <v>342.058368473749</v>
       </c>
-      <c r="J22" s="1">
+      <c r="O22" s="1">
+        <v>3172.8575635847401</v>
+      </c>
+      <c r="P22" s="1">
         <v>55531.209751856397</v>
       </c>
-      <c r="K22" s="1">
+      <c r="Q22" s="1">
         <v>35983.486274115203</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>7</v>
       </c>
@@ -2264,29 +3162,44 @@
       <c r="C23" t="s">
         <v>0</v>
       </c>
-      <c r="E23" s="1">
+      <c r="F23" s="1">
         <v>2056.7785692744501</v>
       </c>
-      <c r="F23" s="1">
+      <c r="G23" s="1">
+        <v>13980.965460842201</v>
+      </c>
+      <c r="H23" s="1">
         <v>18606.703142693601</v>
       </c>
-      <c r="G23" s="1">
-        <v>47811.093394094598</v>
-      </c>
-      <c r="H23" s="1">
+      <c r="I23" s="1">
+        <v>462352.174389127</v>
+      </c>
+      <c r="J23" s="2">
+        <v>23945.8004612939</v>
+      </c>
+      <c r="K23" s="1">
+        <v>102774.84710952399</v>
+      </c>
+      <c r="L23" s="1">
         <v>10066.927515371901</v>
       </c>
-      <c r="I23" s="1">
+      <c r="M23" s="1">
+        <v>220374.78283787699</v>
+      </c>
+      <c r="N23" s="1">
         <v>421.23427726812002</v>
       </c>
-      <c r="J23" s="1">
+      <c r="O23" s="1">
+        <v>5007.5143753383099</v>
+      </c>
+      <c r="P23" s="1">
         <v>52404.222916664497</v>
       </c>
-      <c r="K23" s="1">
+      <c r="Q23" s="1">
         <v>34801.993057920001</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>6</v>
       </c>
@@ -2296,29 +3209,44 @@
       <c r="C24" t="s">
         <v>0</v>
       </c>
-      <c r="E24" s="1">
+      <c r="F24" s="1">
         <v>3182.7540512832602</v>
       </c>
-      <c r="F24" s="1">
+      <c r="G24" s="1">
+        <v>20716.688506052498</v>
+      </c>
+      <c r="H24" s="1">
         <v>29286.974768860899</v>
       </c>
-      <c r="G24" s="1">
-        <v>60906.428978592798</v>
-      </c>
-      <c r="H24" s="1">
+      <c r="I24" s="1">
+        <v>617822.83200470998</v>
+      </c>
+      <c r="J24" s="2">
+        <v>35695.060961856499</v>
+      </c>
+      <c r="K24" s="1">
+        <v>155880.05952328999</v>
+      </c>
+      <c r="L24" s="1">
         <v>9740.8776702336709</v>
       </c>
-      <c r="I24" s="1">
+      <c r="M24" s="1">
+        <v>259070.44044653</v>
+      </c>
+      <c r="N24" s="1">
         <v>1284.67521796611</v>
       </c>
-      <c r="J24" s="1">
+      <c r="O24" s="1">
+        <v>8349.4552475030196</v>
+      </c>
+      <c r="P24" s="1">
         <v>48240.554310301603</v>
       </c>
-      <c r="K24" s="1">
+      <c r="Q24" s="1">
         <v>32727.3315273232</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>5</v>
       </c>
@@ -2328,29 +3256,44 @@
       <c r="C25" t="s">
         <v>0</v>
       </c>
-      <c r="E25" s="1">
+      <c r="F25" s="1">
         <v>4367.2525616008097</v>
       </c>
-      <c r="F25" s="1">
+      <c r="G25" s="1">
+        <v>27968.002455388101</v>
+      </c>
+      <c r="H25" s="1">
         <v>41010.489145052699</v>
       </c>
-      <c r="G25" s="1">
-        <v>68773.167936683807</v>
-      </c>
-      <c r="H25" s="1">
+      <c r="I25" s="1">
+        <v>816928.980863353</v>
+      </c>
+      <c r="J25" s="2">
+        <v>45544.271434501301</v>
+      </c>
+      <c r="K25" s="1">
+        <v>196161.36744029701</v>
+      </c>
+      <c r="L25" s="1">
         <v>7234.7744116886597</v>
       </c>
-      <c r="I25" s="1">
+      <c r="M25" s="1">
+        <v>286839.89297212398</v>
+      </c>
+      <c r="N25" s="1">
         <v>3492.81836113283</v>
       </c>
-      <c r="J25" s="1">
+      <c r="O25" s="1">
+        <v>17813.079513002001</v>
+      </c>
+      <c r="P25" s="1">
         <v>45361.153274361197</v>
       </c>
-      <c r="K25" s="1">
+      <c r="Q25" s="1">
         <v>31382.510572155101</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>4</v>
       </c>
@@ -2360,29 +3303,44 @@
       <c r="C26" t="s">
         <v>0</v>
       </c>
-      <c r="E26" s="1">
+      <c r="F26" s="1">
         <v>4843.49979280359</v>
       </c>
-      <c r="F26" s="1">
+      <c r="G26" s="1">
+        <v>29948.8888437348</v>
+      </c>
+      <c r="H26" s="1">
         <v>41885.195486218399</v>
       </c>
-      <c r="G26" s="1">
-        <v>63162.831196373998</v>
-      </c>
-      <c r="H26" s="1">
+      <c r="I26" s="1">
+        <v>815694.47710130305</v>
+      </c>
+      <c r="J26" s="2">
+        <v>46498.811146259999</v>
+      </c>
+      <c r="K26" s="1">
+        <v>194405.53852473499</v>
+      </c>
+      <c r="L26" s="1">
         <v>3193.9782544847899</v>
       </c>
-      <c r="I26" s="1">
+      <c r="M26" s="1">
+        <v>246569.70954799899</v>
+      </c>
+      <c r="N26" s="1">
         <v>5395.4809739491102</v>
       </c>
-      <c r="J26" s="1">
+      <c r="O26" s="1">
+        <v>30271.4144989058</v>
+      </c>
+      <c r="P26" s="1">
         <v>36008.780525071503</v>
       </c>
-      <c r="K26" s="1">
+      <c r="Q26" s="1">
         <v>24306.229015712201</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>3</v>
       </c>
@@ -2392,29 +3350,44 @@
       <c r="C27" t="s">
         <v>0</v>
       </c>
-      <c r="E27" s="1">
+      <c r="F27" s="1">
         <v>3508.92793544182</v>
       </c>
-      <c r="F27" s="1">
+      <c r="G27" s="1">
+        <v>20107.0071142997</v>
+      </c>
+      <c r="H27" s="1">
         <v>30568.730726834699</v>
       </c>
-      <c r="G27" s="1">
-        <v>43769.993921533402</v>
-      </c>
-      <c r="H27" s="1">
+      <c r="I27" s="1">
+        <v>628614.60481094802</v>
+      </c>
+      <c r="J27" s="2">
+        <v>33496.792099516701</v>
+      </c>
+      <c r="K27" s="1">
+        <v>134407.38222206099</v>
+      </c>
+      <c r="L27" s="1">
         <v>919.29958004632294</v>
       </c>
-      <c r="I27" s="1">
+      <c r="M27" s="1">
+        <v>166885.197406783</v>
+      </c>
+      <c r="N27" s="1">
         <v>6418.6206639030597</v>
       </c>
-      <c r="J27" s="1">
+      <c r="O27" s="1">
+        <v>40493.295002375497</v>
+      </c>
+      <c r="P27" s="1">
         <v>23844.600835253401</v>
       </c>
-      <c r="K27" s="1">
+      <c r="Q27" s="1">
         <v>16784.8676980251</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>2</v>
       </c>
@@ -2424,29 +3397,44 @@
       <c r="C28" t="s">
         <v>0</v>
       </c>
-      <c r="E28" s="1">
+      <c r="F28" s="1">
         <v>3173.3660850716601</v>
       </c>
-      <c r="F28" s="1">
+      <c r="G28" s="1">
+        <v>16236.907614465799</v>
+      </c>
+      <c r="H28" s="1">
         <v>29682.2221039221</v>
       </c>
-      <c r="G28" s="1">
-        <v>33925.402817990798</v>
-      </c>
-      <c r="H28" s="1">
+      <c r="I28" s="1">
+        <v>553497.05804539705</v>
+      </c>
+      <c r="J28" s="2">
+        <v>28486.6502125714</v>
+      </c>
+      <c r="K28" s="1">
+        <v>94485.028821959801</v>
+      </c>
+      <c r="L28" s="1">
         <v>105.886084134353</v>
       </c>
-      <c r="I28" s="1">
+      <c r="M28" s="1">
+        <v>125520.73060958101</v>
+      </c>
+      <c r="N28" s="1">
         <v>9188.4349323497008</v>
       </c>
-      <c r="J28" s="1">
+      <c r="O28" s="1">
+        <v>54483.110206718098</v>
+      </c>
+      <c r="P28" s="1">
         <v>18875.3969379519</v>
       </c>
-      <c r="K28" s="1">
+      <c r="Q28" s="1">
         <v>13090.894410745501</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>1</v>
       </c>
@@ -2456,25 +3444,40 @@
       <c r="C29" t="s">
         <v>0</v>
       </c>
-      <c r="E29" s="1">
+      <c r="F29" s="1">
         <v>2556.4632611894599</v>
       </c>
-      <c r="F29" s="1">
+      <c r="G29" s="1">
+        <v>10674.362873013801</v>
+      </c>
+      <c r="H29" s="1">
         <v>22499.177480744602</v>
       </c>
-      <c r="G29" s="1">
-        <v>21763.281474445499</v>
-      </c>
-      <c r="H29" s="1">
+      <c r="I29" s="1">
+        <v>362956.85810872703</v>
+      </c>
+      <c r="J29" s="2">
+        <v>20103.870500991401</v>
+      </c>
+      <c r="K29" s="1">
+        <v>49515.049817384002</v>
+      </c>
+      <c r="L29" s="1">
         <v>37.156910532311599</v>
       </c>
-      <c r="I29" s="1">
+      <c r="M29" s="1">
+        <v>72808.894138648495</v>
+      </c>
+      <c r="N29" s="1">
         <v>8750.47364491589</v>
       </c>
-      <c r="J29" s="1">
+      <c r="O29" s="1">
+        <v>52544.6702693021</v>
+      </c>
+      <c r="P29" s="1">
         <v>12144.0385964947</v>
       </c>
-      <c r="K29" s="1">
+      <c r="Q29" s="1">
         <v>7989.5474402997597</v>
       </c>
     </row>
@@ -2485,20 +3488,26 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9F9C405-CC78-DE47-80BA-51DD73EFCA1A}">
-  <dimension ref="A1:K29"/>
+  <dimension ref="A1:Q32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="4" max="4" width="11.5" customWidth="1"/>
-    <col min="5" max="5" width="12" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.83203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.5" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.5" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.83203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.83203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.6640625" customWidth="1"/>
+    <col min="12" max="12" width="14.5" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.5" customWidth="1"/>
+    <col min="14" max="14" width="13.5" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.5" customWidth="1"/>
+    <col min="16" max="16" width="13" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>23</v>
       </c>
@@ -2512,28 +3521,46 @@
         <v>25</v>
       </c>
       <c r="E1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" t="s">
         <v>26</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H1" t="s">
         <v>19</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
+        <v>29</v>
+      </c>
+      <c r="J1" t="s">
         <v>17</v>
       </c>
-      <c r="H1" t="s">
+      <c r="K1" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1" t="s">
         <v>18</v>
       </c>
-      <c r="I1" t="s">
+      <c r="M1" t="s">
+        <v>31</v>
+      </c>
+      <c r="N1" t="s">
         <v>20</v>
       </c>
-      <c r="J1" t="s">
+      <c r="O1" t="s">
+        <v>32</v>
+      </c>
+      <c r="P1" t="s">
         <v>16</v>
       </c>
-      <c r="K1" t="s">
+      <c r="Q1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -2547,28 +3574,46 @@
         <v>59.804399829096397</v>
       </c>
       <c r="E2" s="1">
+        <v>528.61862994651904</v>
+      </c>
+      <c r="F2" s="1">
         <v>39.558076580761004</v>
       </c>
-      <c r="F2" s="1">
+      <c r="G2" s="1">
+        <v>306.62077663792701</v>
+      </c>
+      <c r="H2" s="1">
         <v>642.129110645482</v>
       </c>
-      <c r="G2" s="1">
-        <v>45101.689759668297</v>
-      </c>
-      <c r="H2" s="1">
+      <c r="I2" s="2">
+        <v>30790</v>
+      </c>
+      <c r="J2" s="2">
+        <v>911.45138711541097</v>
+      </c>
+      <c r="K2" s="2">
+        <v>6908</v>
+      </c>
+      <c r="L2" s="1">
         <v>2523.74999829432</v>
       </c>
-      <c r="I2" s="1">
-        <v>0</v>
-      </c>
-      <c r="J2" s="1">
+      <c r="M2" s="2">
+        <v>14173</v>
+      </c>
+      <c r="N2" s="1">
+        <v>0</v>
+      </c>
+      <c r="O2" s="2">
+        <v>0</v>
+      </c>
+      <c r="P2" s="1">
         <v>138801.978834651</v>
       </c>
-      <c r="K2" s="1">
+      <c r="Q2" s="1">
         <v>79621.9456363192</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -2582,28 +3627,46 @@
         <v>338.75419398620102</v>
       </c>
       <c r="E3" s="1">
+        <v>2874.5933477784101</v>
+      </c>
+      <c r="F3" s="1">
         <v>65.571164526666095</v>
       </c>
-      <c r="F3" s="1">
+      <c r="G3" s="1">
+        <v>518.35393398384895</v>
+      </c>
+      <c r="H3" s="1">
         <v>835.24767500852295</v>
       </c>
-      <c r="G3" s="1">
-        <v>64924.075297868498</v>
-      </c>
-      <c r="H3" s="1">
+      <c r="I3" s="2">
+        <v>44617</v>
+      </c>
+      <c r="J3" s="2">
+        <v>1703.9853805164601</v>
+      </c>
+      <c r="K3" s="2">
+        <v>13156</v>
+      </c>
+      <c r="L3" s="1">
         <v>3002.3680942698702</v>
       </c>
-      <c r="I3">
-        <v>0</v>
-      </c>
-      <c r="J3" s="1">
+      <c r="M3" s="2">
+        <v>28524</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3" s="2">
+        <v>0</v>
+      </c>
+      <c r="P3" s="1">
         <v>134334.177423841</v>
       </c>
-      <c r="K3" s="1">
+      <c r="Q3" s="1">
         <v>80433.486807937195</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -2617,28 +3680,46 @@
         <v>1099.1886487762899</v>
       </c>
       <c r="E4" s="1">
+        <v>9625.9312430198206</v>
+      </c>
+      <c r="F4" s="1">
         <v>148.46584721539801</v>
       </c>
-      <c r="F4" s="1">
+      <c r="G4" s="1">
+        <v>1138.84623665087</v>
+      </c>
+      <c r="H4" s="1">
         <v>1167.13932798873</v>
       </c>
-      <c r="G4" s="1">
-        <v>81735.535434642006</v>
-      </c>
-      <c r="H4" s="1">
+      <c r="I4" s="2">
+        <v>76829</v>
+      </c>
+      <c r="J4" s="2">
+        <v>3457.61814189396</v>
+      </c>
+      <c r="K4" s="2">
+        <v>26550</v>
+      </c>
+      <c r="L4" s="1">
         <v>3660.9913132224701</v>
       </c>
-      <c r="I4">
-        <v>0</v>
-      </c>
-      <c r="J4" s="1">
+      <c r="M4" s="2">
+        <v>45735</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4" s="2">
+        <v>0</v>
+      </c>
+      <c r="P4" s="1">
         <v>135290.46076181901</v>
       </c>
-      <c r="K4" s="1">
+      <c r="Q4" s="1">
         <v>84230.089263609596</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>11</v>
       </c>
@@ -2652,28 +3733,46 @@
         <v>2160.8757418802202</v>
       </c>
       <c r="E5" s="1">
+        <v>19205.733763996301</v>
+      </c>
+      <c r="F5" s="1">
         <v>271.695847512353</v>
       </c>
-      <c r="F5" s="1">
+      <c r="G5" s="1">
+        <v>2137.56955856779</v>
+      </c>
+      <c r="H5" s="1">
         <v>1684.4540816368401</v>
       </c>
-      <c r="G5" s="1">
-        <v>100870.669712984</v>
-      </c>
-      <c r="H5" s="1">
+      <c r="I5" s="2">
+        <v>100371</v>
+      </c>
+      <c r="J5" s="2">
+        <v>5803.5784248083601</v>
+      </c>
+      <c r="K5" s="2">
+        <v>43817</v>
+      </c>
+      <c r="L5" s="1">
         <v>4654.6955970973604</v>
       </c>
-      <c r="I5">
-        <v>0</v>
-      </c>
-      <c r="J5" s="1">
+      <c r="M5" s="2">
+        <v>64086</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5" s="2">
+        <v>0</v>
+      </c>
+      <c r="P5" s="1">
         <v>138678.74731181099</v>
       </c>
-      <c r="K5" s="1">
+      <c r="Q5" s="1">
         <v>86067.449018426298</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -2687,28 +3786,46 @@
         <v>4034.4713182320102</v>
       </c>
       <c r="E6" s="1">
+        <v>36674.268882387703</v>
+      </c>
+      <c r="F6" s="1">
         <v>478.803499594897</v>
       </c>
-      <c r="F6" s="1">
+      <c r="G6" s="1">
+        <v>3608.9620557983999</v>
+      </c>
+      <c r="H6" s="1">
         <v>3726.8103490562698</v>
       </c>
-      <c r="G6" s="1">
-        <v>111586.798374929</v>
-      </c>
-      <c r="H6" s="1">
+      <c r="I6" s="2">
+        <v>182730</v>
+      </c>
+      <c r="J6" s="2">
+        <v>9083.6558376520406</v>
+      </c>
+      <c r="K6" s="2">
+        <v>69188</v>
+      </c>
+      <c r="L6" s="1">
         <v>5163.1622850513504</v>
       </c>
-      <c r="I6" s="1">
+      <c r="M6" s="2">
+        <v>84285</v>
+      </c>
+      <c r="N6" s="1">
         <v>339.387898639561</v>
       </c>
-      <c r="J6" s="1">
+      <c r="O6" s="2">
+        <v>562</v>
+      </c>
+      <c r="P6" s="1">
         <v>136953.78567725999</v>
       </c>
-      <c r="K6" s="1">
+      <c r="Q6" s="1">
         <v>89640.730596265406</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -2722,28 +3839,46 @@
         <v>6448.6304587740196</v>
       </c>
       <c r="E7" s="1">
+        <v>59496.746987182603</v>
+      </c>
+      <c r="F7" s="1">
         <v>935.16127254529101</v>
       </c>
-      <c r="F7" s="1">
+      <c r="G7" s="1">
+        <v>6992.1600255153899</v>
+      </c>
+      <c r="H7" s="1">
         <v>6962.4320982106001</v>
       </c>
-      <c r="G7" s="1">
-        <v>140738.44331002099</v>
-      </c>
-      <c r="H7" s="1">
+      <c r="I7" s="2">
+        <v>313271</v>
+      </c>
+      <c r="J7" s="2">
+        <v>14854.559367494699</v>
+      </c>
+      <c r="K7" s="2">
+        <v>111612</v>
+      </c>
+      <c r="L7" s="1">
         <v>6694.3701977393903</v>
       </c>
-      <c r="I7" s="1">
+      <c r="M7" s="2">
+        <v>113965</v>
+      </c>
+      <c r="N7" s="1">
         <v>838.63762340512596</v>
       </c>
-      <c r="J7" s="1">
+      <c r="O7" s="2">
+        <v>3491</v>
+      </c>
+      <c r="P7" s="1">
         <v>145904.23741587199</v>
       </c>
-      <c r="K7" s="1">
+      <c r="Q7" s="1">
         <v>93555.262635121806</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -2757,28 +3892,46 @@
         <v>7539.1352370761797</v>
       </c>
       <c r="E8" s="1">
+        <v>72383.254923575994</v>
+      </c>
+      <c r="F8" s="1">
         <v>1409.87727722094</v>
       </c>
-      <c r="F8" s="1">
+      <c r="G8" s="1">
+        <v>10378.556069021301</v>
+      </c>
+      <c r="H8" s="1">
         <v>10496.916387537</v>
       </c>
-      <c r="G8" s="1">
-        <v>144889.84020291499</v>
-      </c>
-      <c r="H8" s="1">
+      <c r="I8" s="2">
+        <v>438184</v>
+      </c>
+      <c r="J8" s="2">
+        <v>18879.301184144901</v>
+      </c>
+      <c r="K8" s="2">
+        <v>138839</v>
+      </c>
+      <c r="L8" s="1">
         <v>9029.3727817545896</v>
       </c>
-      <c r="I8" s="1">
+      <c r="M8" s="2">
+        <v>139435</v>
+      </c>
+      <c r="N8" s="1">
         <v>1030.3448775004799</v>
       </c>
-      <c r="J8" s="1">
+      <c r="O8" s="2">
+        <v>7204</v>
+      </c>
+      <c r="P8" s="1">
         <v>146698.36388370799</v>
       </c>
-      <c r="K8" s="1">
+      <c r="Q8" s="1">
         <v>98613.814029934598</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -2792,28 +3945,46 @@
         <v>7783.4596160726596</v>
       </c>
       <c r="E9" s="1">
+        <v>81609.736096332999</v>
+      </c>
+      <c r="F9" s="1">
         <v>1950.31315103461</v>
       </c>
-      <c r="F9" s="1">
+      <c r="G9" s="1">
+        <v>14021.960996878201</v>
+      </c>
+      <c r="H9" s="1">
         <v>17270.020826055301</v>
       </c>
-      <c r="G9" s="1">
-        <v>144759.89546308201</v>
-      </c>
-      <c r="H9" s="1">
+      <c r="I9" s="2">
+        <v>547002</v>
+      </c>
+      <c r="J9" s="2">
+        <v>22800.713382451198</v>
+      </c>
+      <c r="K9" s="2">
+        <v>163681</v>
+      </c>
+      <c r="L9" s="1">
         <v>12517.466134808101</v>
       </c>
-      <c r="I9" s="1">
+      <c r="M9" s="2">
+        <v>178210</v>
+      </c>
+      <c r="N9" s="1">
         <v>1405.4112792992701</v>
       </c>
-      <c r="J9" s="1">
+      <c r="O9" s="2">
+        <v>10355</v>
+      </c>
+      <c r="P9" s="1">
         <v>139865.58457303501</v>
       </c>
-      <c r="K9" s="1">
+      <c r="Q9" s="1">
         <v>97260.106005538793</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>6</v>
       </c>
@@ -2827,28 +3998,46 @@
         <v>8682.5409281786397</v>
       </c>
       <c r="E10" s="1">
+        <v>97088.724916336098</v>
+      </c>
+      <c r="F10" s="1">
         <v>2659.8364690378298</v>
       </c>
-      <c r="F10" s="1">
+      <c r="G10" s="1">
+        <v>18748.1676267947</v>
+      </c>
+      <c r="H10" s="1">
         <v>26222.9007885106</v>
       </c>
-      <c r="G10" s="1">
-        <v>137165.71236874399</v>
-      </c>
-      <c r="H10" s="1">
+      <c r="I10" s="2">
+        <v>646816</v>
+      </c>
+      <c r="J10" s="2">
+        <v>27848.5981868241</v>
+      </c>
+      <c r="K10" s="2">
+        <v>194870</v>
+      </c>
+      <c r="L10" s="1">
         <v>12913.7106924167</v>
       </c>
-      <c r="I10" s="1">
+      <c r="M10" s="2">
+        <v>225220</v>
+      </c>
+      <c r="N10" s="1">
         <v>3133.34653567033</v>
       </c>
-      <c r="J10" s="1">
+      <c r="O10" s="2">
+        <v>16305</v>
+      </c>
+      <c r="P10" s="1">
         <v>138761.047798849</v>
       </c>
-      <c r="K10" s="1">
+      <c r="Q10" s="1">
         <v>95299.347541525305</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>5</v>
       </c>
@@ -2862,28 +4051,46 @@
         <v>9419.7461775662505</v>
       </c>
       <c r="E11" s="1">
+        <v>109851.431427342</v>
+      </c>
+      <c r="F11" s="1">
         <v>3469.3239358794799</v>
       </c>
-      <c r="F11" s="1">
+      <c r="G11" s="1">
+        <v>23941.239652184198</v>
+      </c>
+      <c r="H11" s="1">
         <v>42073.098996386798</v>
       </c>
-      <c r="G11" s="1">
-        <v>128392.78024285</v>
-      </c>
-      <c r="H11" s="1">
+      <c r="I11" s="2">
+        <v>867875</v>
+      </c>
+      <c r="J11" s="2">
+        <v>32827.296104032102</v>
+      </c>
+      <c r="K11" s="2">
+        <v>220975</v>
+      </c>
+      <c r="L11" s="1">
         <v>11900.0316725886</v>
       </c>
-      <c r="I11" s="1">
+      <c r="M11" s="2">
+        <v>263484</v>
+      </c>
+      <c r="N11" s="1">
         <v>7203.4588355820897</v>
       </c>
-      <c r="J11" s="1">
+      <c r="O11" s="2">
+        <v>33390</v>
+      </c>
+      <c r="P11" s="1">
         <v>142257.93824029199</v>
       </c>
-      <c r="K11" s="1">
+      <c r="Q11" s="1">
         <v>92332.258729937996</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>4</v>
       </c>
@@ -2897,28 +4104,46 @@
         <v>8392.0729819998396</v>
       </c>
       <c r="E12" s="1">
+        <v>97789.832297061803</v>
+      </c>
+      <c r="F12" s="1">
         <v>4016.4858490390998</v>
       </c>
-      <c r="F12" s="1">
+      <c r="G12" s="1">
+        <v>26942.591675385898</v>
+      </c>
+      <c r="H12" s="1">
         <v>45614.958709516002</v>
       </c>
-      <c r="G12" s="1">
-        <v>100310.28210771301</v>
-      </c>
-      <c r="H12" s="1">
+      <c r="I12" s="2">
+        <v>867903</v>
+      </c>
+      <c r="J12" s="2">
+        <v>32702.252889076299</v>
+      </c>
+      <c r="K12" s="2">
+        <v>211115</v>
+      </c>
+      <c r="L12" s="1">
         <v>7616.1550117172501</v>
       </c>
-      <c r="I12" s="1">
+      <c r="M12" s="2">
+        <v>242727</v>
+      </c>
+      <c r="N12" s="1">
         <v>12288.5092118624</v>
       </c>
-      <c r="J12" s="1">
+      <c r="O12" s="2">
+        <v>58299</v>
+      </c>
+      <c r="P12" s="1">
         <v>118913.54042939701</v>
       </c>
-      <c r="K12" s="1">
+      <c r="Q12" s="1">
         <v>79845.600196532905</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>3</v>
       </c>
@@ -2932,28 +4157,46 @@
         <v>5605.4318767363702</v>
       </c>
       <c r="E13" s="1">
+        <v>69054.518164990601</v>
+      </c>
+      <c r="F13" s="1">
         <v>3581.1551481731099</v>
       </c>
-      <c r="F13" s="1">
+      <c r="G13" s="1">
+        <v>23150.792765775899</v>
+      </c>
+      <c r="H13" s="1">
         <v>44305.570506391399</v>
       </c>
-      <c r="G13" s="1">
-        <v>57311.304626032499</v>
-      </c>
-      <c r="H13" s="1">
+      <c r="I13" s="2">
+        <v>742889</v>
+      </c>
+      <c r="J13" s="2">
+        <v>25750.333296566201</v>
+      </c>
+      <c r="K13" s="2">
+        <v>154029</v>
+      </c>
+      <c r="L13" s="1">
         <v>2187.2252600194101</v>
       </c>
-      <c r="I13" s="1">
+      <c r="M13" s="2">
+        <v>183929</v>
+      </c>
+      <c r="N13" s="1">
         <v>17006.707577093199</v>
       </c>
-      <c r="J13" s="1">
+      <c r="O13" s="2">
+        <v>84819</v>
+      </c>
+      <c r="P13" s="1">
         <v>84294.887451215094</v>
       </c>
-      <c r="K13" s="1">
+      <c r="Q13" s="1">
         <v>58632.261798236999</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>2</v>
       </c>
@@ -2967,28 +4210,46 @@
         <v>5646.2836974170305</v>
       </c>
       <c r="E14" s="1">
+        <v>67036.943439962502</v>
+      </c>
+      <c r="F14" s="1">
         <v>4613.8355980015103</v>
       </c>
-      <c r="F14" s="1">
+      <c r="G14" s="1">
+        <v>26114.553177540001</v>
+      </c>
+      <c r="H14" s="1">
         <v>49483.565136865298</v>
       </c>
-      <c r="G14" s="1">
-        <v>49737.344193223798</v>
-      </c>
-      <c r="H14" s="1">
+      <c r="I14" s="2">
+        <v>769875</v>
+      </c>
+      <c r="J14" s="2">
+        <v>28486.4323472213</v>
+      </c>
+      <c r="K14" s="2">
+        <v>149280</v>
+      </c>
+      <c r="L14" s="1">
         <v>589.961836999159</v>
       </c>
-      <c r="I14" s="1">
+      <c r="M14" s="2">
+        <v>165061</v>
+      </c>
+      <c r="N14" s="1">
         <v>26251.522138160799</v>
       </c>
-      <c r="J14" s="1">
+      <c r="O14" s="2">
+        <v>135968</v>
+      </c>
+      <c r="P14" s="1">
         <v>78378.019836771899</v>
       </c>
-      <c r="K14" s="1">
+      <c r="Q14" s="1">
         <v>55905.972149341003</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>1</v>
       </c>
@@ -3002,28 +4263,46 @@
         <v>4837.96788784605</v>
       </c>
       <c r="E15" s="1">
+        <v>53317.721085799501</v>
+      </c>
+      <c r="F15" s="1">
         <v>4512.5928895033103</v>
       </c>
-      <c r="F15" s="1">
+      <c r="G15" s="1">
+        <v>21121.6603632894</v>
+      </c>
+      <c r="H15" s="1">
         <v>50726.232449147203</v>
       </c>
-      <c r="G15" s="1">
-        <v>35934.197858170097</v>
-      </c>
-      <c r="H15" s="1">
+      <c r="I15" s="2">
+        <v>672152</v>
+      </c>
+      <c r="J15" s="2">
+        <v>25089.019079394999</v>
+      </c>
+      <c r="K15" s="2">
+        <v>113083</v>
+      </c>
+      <c r="L15" s="1">
         <v>252.87416136956799</v>
       </c>
-      <c r="I15" s="1">
+      <c r="M15" s="2">
+        <v>122543</v>
+      </c>
+      <c r="N15" s="1">
         <v>29294.222935033202</v>
       </c>
-      <c r="J15" s="1">
+      <c r="O15" s="2">
+        <v>161047</v>
+      </c>
+      <c r="P15" s="1">
         <v>60698.698858546697</v>
       </c>
-      <c r="K15" s="1">
+      <c r="Q15" s="1">
         <v>46098.252192666499</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>14</v>
       </c>
@@ -3033,29 +4312,44 @@
       <c r="C16" t="s">
         <v>0</v>
       </c>
-      <c r="E16" s="1">
+      <c r="F16" s="1">
         <v>47.422020467506997</v>
       </c>
-      <c r="F16" s="1">
+      <c r="G16" s="1">
+        <v>367.87494172381599</v>
+      </c>
+      <c r="H16" s="1">
         <v>1347.3945715340301</v>
       </c>
-      <c r="G16" s="1">
-        <v>15262.467575066201</v>
-      </c>
-      <c r="H16" s="1">
+      <c r="I16" s="1">
+        <v>26533.785265621402</v>
+      </c>
+      <c r="J16" s="2">
+        <v>1316.05074652953</v>
+      </c>
+      <c r="K16" s="1">
+        <v>10258.2666324114</v>
+      </c>
+      <c r="L16" s="1">
         <v>3799.4856851865602</v>
       </c>
-      <c r="I16">
-        <v>0</v>
-      </c>
-      <c r="J16" s="1">
+      <c r="M16" s="1">
+        <v>20668.953062844401</v>
+      </c>
+      <c r="N16">
+        <v>0</v>
+      </c>
+      <c r="O16" s="2">
+        <v>0</v>
+      </c>
+      <c r="P16" s="1">
         <v>79932.820095374904</v>
       </c>
-      <c r="K16" s="1">
+      <c r="Q16" s="1">
         <v>47283.987962690298</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>13</v>
       </c>
@@ -3065,29 +4359,44 @@
       <c r="C17" t="s">
         <v>0</v>
       </c>
-      <c r="E17" s="1">
+      <c r="F17" s="1">
         <v>78.367669383549995</v>
       </c>
-      <c r="F17" s="1">
+      <c r="G17" s="1">
+        <v>594.67950785223195</v>
+      </c>
+      <c r="H17" s="1">
         <v>1649.9146067435099</v>
       </c>
-      <c r="G17" s="1">
-        <v>17262.374967923501</v>
-      </c>
-      <c r="H17" s="1">
+      <c r="I17" s="1">
+        <v>39324.3863430415</v>
+      </c>
+      <c r="J17" s="2">
+        <v>2196.53421089822</v>
+      </c>
+      <c r="K17" s="1">
+        <v>17197.497781866299</v>
+      </c>
+      <c r="L17" s="1">
         <v>4799.7685902288704</v>
       </c>
-      <c r="I17">
-        <v>0</v>
-      </c>
-      <c r="J17" s="1">
+      <c r="M17" s="1">
+        <v>39968.697674577699</v>
+      </c>
+      <c r="N17">
+        <v>0</v>
+      </c>
+      <c r="O17" s="2">
+        <v>0</v>
+      </c>
+      <c r="P17" s="1">
         <v>75294.311268587902</v>
       </c>
-      <c r="K17" s="1">
+      <c r="Q17" s="1">
         <v>47088.315859173301</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>12</v>
       </c>
@@ -3097,29 +4406,44 @@
       <c r="C18" t="s">
         <v>0</v>
       </c>
-      <c r="E18" s="1">
+      <c r="F18" s="1">
         <v>208.42688819551</v>
       </c>
-      <c r="F18" s="1">
+      <c r="G18" s="1">
+        <v>1600.38187527372</v>
+      </c>
+      <c r="H18" s="1">
         <v>2371.2075734478499</v>
       </c>
-      <c r="G18" s="1">
-        <v>22088.826810386101</v>
-      </c>
-      <c r="H18" s="1">
+      <c r="I18" s="1">
+        <v>68252.026161493093</v>
+      </c>
+      <c r="J18" s="2">
+        <v>3444.7688849627998</v>
+      </c>
+      <c r="K18" s="1">
+        <v>26169.860705836101</v>
+      </c>
+      <c r="L18" s="1">
         <v>6413.2160890507603</v>
       </c>
-      <c r="I18">
-        <v>0</v>
-      </c>
-      <c r="J18" s="1">
+      <c r="M18" s="1">
+        <v>67895.561916907405</v>
+      </c>
+      <c r="N18">
+        <v>0</v>
+      </c>
+      <c r="O18" s="2">
+        <v>0</v>
+      </c>
+      <c r="P18" s="1">
         <v>74562.117488012795</v>
       </c>
-      <c r="K18" s="1">
+      <c r="Q18" s="1">
         <v>48856.6953063236</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>11</v>
       </c>
@@ -3129,29 +4453,44 @@
       <c r="C19" t="s">
         <v>0</v>
       </c>
-      <c r="E19" s="1">
+      <c r="F19" s="1">
         <v>317.170981278905</v>
       </c>
-      <c r="F19" s="1">
+      <c r="G19" s="1">
+        <v>2425.2424661914201</v>
+      </c>
+      <c r="H19" s="1">
         <v>3615.3864966910901</v>
       </c>
-      <c r="G19" s="1">
-        <v>28666.023924118301</v>
-      </c>
-      <c r="H19" s="1">
+      <c r="I19" s="1">
+        <v>121852.52428962399</v>
+      </c>
+      <c r="J19" s="2">
+        <v>4669.1976745108104</v>
+      </c>
+      <c r="K19" s="1">
+        <v>32467.9396254161</v>
+      </c>
+      <c r="L19" s="1">
         <v>8418.2629535505694</v>
       </c>
-      <c r="I19">
-        <v>0</v>
-      </c>
-      <c r="J19" s="1">
+      <c r="M19" s="1">
+        <v>99779.437044506398</v>
+      </c>
+      <c r="N19">
+        <v>0</v>
+      </c>
+      <c r="O19" s="2">
+        <v>0</v>
+      </c>
+      <c r="P19" s="1">
         <v>77561.278356379102</v>
       </c>
-      <c r="K19" s="1">
+      <c r="Q19" s="1">
         <v>49788.700798170998</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>10</v>
       </c>
@@ -3161,29 +4500,44 @@
       <c r="C20" t="s">
         <v>0</v>
       </c>
-      <c r="E20" s="1">
+      <c r="F20" s="1">
         <v>471.48268342005099</v>
       </c>
-      <c r="F20" s="1">
+      <c r="G20" s="1">
+        <v>3611.6191542491401</v>
+      </c>
+      <c r="H20" s="1">
         <v>6517.7431013639898</v>
       </c>
-      <c r="G20" s="1">
-        <v>33451.674914397699</v>
-      </c>
-      <c r="H20" s="1">
+      <c r="I20" s="1">
+        <v>236104.340624862</v>
+      </c>
+      <c r="J20" s="2">
+        <v>6209.7168937659999</v>
+      </c>
+      <c r="K20" s="1">
+        <v>40079.008120369297</v>
+      </c>
+      <c r="L20" s="1">
         <v>9649.9671734145595</v>
       </c>
-      <c r="I20" s="1">
+      <c r="M20" s="1">
+        <v>139221.82033936901</v>
+      </c>
+      <c r="N20" s="1">
         <v>304.33648533112603</v>
       </c>
-      <c r="J20" s="1">
+      <c r="O20" s="2">
+        <v>507</v>
+      </c>
+      <c r="P20" s="1">
         <v>75885.270495522505</v>
       </c>
-      <c r="K20" s="1">
+      <c r="Q20" s="1">
         <v>51466.440542918303</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>9</v>
       </c>
@@ -3193,29 +4547,44 @@
       <c r="C21" t="s">
         <v>0</v>
       </c>
-      <c r="E21" s="1">
+      <c r="F21" s="1">
         <v>999.92422027439795</v>
       </c>
-      <c r="F21" s="1">
+      <c r="G21" s="1">
+        <v>7438.8047618827604</v>
+      </c>
+      <c r="H21" s="1">
         <v>11825.4136507613</v>
       </c>
-      <c r="G21" s="1">
-        <v>50711.385527780702</v>
-      </c>
-      <c r="H21" s="1">
+      <c r="I21" s="1">
+        <v>368986.80180305301</v>
+      </c>
+      <c r="J21" s="2">
+        <v>11189.973906531</v>
+      </c>
+      <c r="K21" s="1">
+        <v>69371.004968649999</v>
+      </c>
+      <c r="L21" s="1">
         <v>12117.2445017883</v>
       </c>
-      <c r="I21" s="1">
+      <c r="M21" s="1">
+        <v>191502.40033358501</v>
+      </c>
+      <c r="N21" s="1">
         <v>730.47820433884601</v>
       </c>
-      <c r="J21" s="1">
+      <c r="O21" s="2">
+        <v>3124</v>
+      </c>
+      <c r="P21" s="1">
         <v>79983.308623345103</v>
       </c>
-      <c r="K21" s="1">
+      <c r="Q21" s="1">
         <v>53178.667848150399</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>8</v>
       </c>
@@ -3225,29 +4594,44 @@
       <c r="C22" t="s">
         <v>0</v>
       </c>
-      <c r="E22" s="1">
+      <c r="F22" s="1">
         <v>1805.2418194035799</v>
       </c>
-      <c r="F22" s="1">
+      <c r="G22" s="1">
+        <v>12961.4911048782</v>
+      </c>
+      <c r="H22" s="1">
         <v>18114.1294362927</v>
       </c>
-      <c r="G22" s="1">
-        <v>62394.887720340397</v>
-      </c>
-      <c r="H22" s="1">
+      <c r="I22" s="1">
+        <v>507608.367886263</v>
+      </c>
+      <c r="J22" s="2">
+        <v>17736.1630231575</v>
+      </c>
+      <c r="K22" s="1">
+        <v>105191.255452565</v>
+      </c>
+      <c r="L22" s="1">
         <v>13849.6866874922</v>
       </c>
-      <c r="I22" s="1">
+      <c r="M22" s="1">
+        <v>237955.51460245499</v>
+      </c>
+      <c r="N22" s="1">
         <v>886.98284525974498</v>
       </c>
-      <c r="J22" s="1">
+      <c r="O22" s="2">
+        <v>6093</v>
+      </c>
+      <c r="P22" s="1">
         <v>77694.023051982906</v>
       </c>
-      <c r="K22" s="1">
+      <c r="Q22" s="1">
         <v>52582.551384206199</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>7</v>
       </c>
@@ -3257,29 +4641,44 @@
       <c r="C23" t="s">
         <v>0</v>
       </c>
-      <c r="E23" s="1">
+      <c r="F23" s="1">
         <v>2671.2234148494899</v>
       </c>
-      <c r="F23" s="1">
+      <c r="G23" s="1">
+        <v>18698.8047758674</v>
+      </c>
+      <c r="H23" s="1">
         <v>28165.924911537699</v>
       </c>
-      <c r="G23" s="1">
-        <v>79332.442986173002</v>
-      </c>
-      <c r="H23" s="1">
+      <c r="I23" s="1">
+        <v>689965.695978162</v>
+      </c>
+      <c r="J23" s="2">
+        <v>27593.2554598442</v>
+      </c>
+      <c r="K23" s="1">
+        <v>159043.565770288</v>
+      </c>
+      <c r="L23" s="1">
         <v>17086.024151701298</v>
       </c>
-      <c r="I23" s="1">
+      <c r="M23" s="1">
+        <v>283071.17981082899</v>
+      </c>
+      <c r="N23" s="1">
         <v>1245.8545953625801</v>
       </c>
-      <c r="J23" s="1">
+      <c r="O23" s="2">
+        <v>8848</v>
+      </c>
+      <c r="P23" s="1">
         <v>71221.094453531696</v>
       </c>
-      <c r="K23" s="1">
+      <c r="Q23" s="1">
         <v>50016.900051043202</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>6</v>
       </c>
@@ -3289,29 +4688,44 @@
       <c r="C24" t="s">
         <v>0</v>
       </c>
-      <c r="E24" s="1">
+      <c r="F24" s="1">
         <v>4084.6148100093701</v>
       </c>
-      <c r="F24" s="1">
+      <c r="G24" s="1">
+        <v>27890.4757061372</v>
+      </c>
+      <c r="H24" s="1">
         <v>39976.591433394096</v>
       </c>
-      <c r="G24" s="1">
-        <v>93784.351040393201</v>
-      </c>
-      <c r="H24" s="1">
+      <c r="I24" s="1">
+        <v>846466.11973423196</v>
+      </c>
+      <c r="J24" s="2">
+        <v>40956.001362257201</v>
+      </c>
+      <c r="K24" s="1">
+        <v>240231.94304821701</v>
+      </c>
+      <c r="L24" s="1">
         <v>15428.0057651596</v>
       </c>
-      <c r="I24" s="1">
+      <c r="M24" s="1">
+        <v>318924.75637703302</v>
+      </c>
+      <c r="N24" s="1">
         <v>2838.05794219465</v>
       </c>
-      <c r="J24" s="1">
+      <c r="O24" s="2">
+        <v>13780</v>
+      </c>
+      <c r="P24" s="1">
         <v>67354.644457613598</v>
       </c>
-      <c r="K24" s="1">
+      <c r="Q24" s="1">
         <v>45813.211646001699</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>5</v>
       </c>
@@ -3321,29 +4735,44 @@
       <c r="C25" t="s">
         <v>0</v>
       </c>
-      <c r="E25" s="1">
+      <c r="F25" s="1">
         <v>5609.2200905805203</v>
       </c>
-      <c r="F25" s="1">
+      <c r="G25" s="1">
+        <v>37324.446845030601</v>
+      </c>
+      <c r="H25" s="1">
         <v>59567.671669830503</v>
       </c>
-      <c r="G25" s="1">
-        <v>112349.387242595</v>
-      </c>
-      <c r="H25" s="1">
+      <c r="I25" s="1">
+        <v>1093502.68593623</v>
+      </c>
+      <c r="J25" s="2">
+        <v>52752.514802457699</v>
+      </c>
+      <c r="K25" s="1">
+        <v>298190.87691749498</v>
+      </c>
+      <c r="L25" s="1">
         <v>12945.5492635112</v>
       </c>
-      <c r="I25" s="1">
+      <c r="M25" s="1">
+        <v>349270.727965436</v>
+      </c>
+      <c r="N25" s="1">
         <v>6364.5755757529396</v>
       </c>
-      <c r="J25" s="1">
+      <c r="O25" s="2">
+        <v>28118</v>
+      </c>
+      <c r="P25" s="1">
         <v>67257.735444433099</v>
       </c>
-      <c r="K25" s="1">
+      <c r="Q25" s="1">
         <v>43471.406191182097</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>4</v>
       </c>
@@ -3353,29 +4782,44 @@
       <c r="C26" t="s">
         <v>0</v>
       </c>
-      <c r="E26" s="1">
+      <c r="F26" s="1">
         <v>6253.7763322601904</v>
       </c>
-      <c r="F26" s="1">
+      <c r="G26" s="1">
+        <v>40194.129721405399</v>
+      </c>
+      <c r="H26" s="1">
         <v>56711.031005466997</v>
       </c>
-      <c r="G26" s="1">
-        <v>98582.7432954994</v>
-      </c>
-      <c r="H26" s="1">
+      <c r="I26" s="1">
+        <v>1004537.12063025</v>
+      </c>
+      <c r="J26" s="2">
+        <v>53310.207803500401</v>
+      </c>
+      <c r="K26" s="1">
+        <v>291736.50862580899</v>
+      </c>
+      <c r="L26" s="1">
         <v>7729.5594035261802</v>
       </c>
-      <c r="I26" s="1">
+      <c r="M26" s="1">
+        <v>295768.04117685102</v>
+      </c>
+      <c r="N26" s="1">
         <v>9780.1680736949093</v>
       </c>
-      <c r="J26" s="1">
+      <c r="O26" s="2">
+        <v>47485</v>
+      </c>
+      <c r="P26" s="1">
         <v>53498.621752128704</v>
       </c>
-      <c r="K26" s="1">
+      <c r="Q26" s="1">
         <v>36043.679827715503</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>3</v>
       </c>
@@ -3385,29 +4829,44 @@
       <c r="C27" t="s">
         <v>0</v>
       </c>
-      <c r="E27" s="1">
+      <c r="F27" s="1">
         <v>4532.96721031982</v>
       </c>
-      <c r="F27" s="1">
+      <c r="G27" s="1">
+        <v>27618.253620618401</v>
+      </c>
+      <c r="H27" s="1">
         <v>44998.082220413002</v>
       </c>
-      <c r="G27" s="1">
-        <v>62034.502835804902</v>
-      </c>
-      <c r="H27" s="1">
+      <c r="I27" s="1">
+        <v>751745.05515120202</v>
+      </c>
+      <c r="J27" s="2">
+        <v>38172.486115264001</v>
+      </c>
+      <c r="K27" s="1">
+        <v>196666.25505651301</v>
+      </c>
+      <c r="L27" s="1">
         <v>1873.36497002801</v>
       </c>
-      <c r="I27" s="1">
+      <c r="M27" s="1">
+        <v>204000.74021801699</v>
+      </c>
+      <c r="N27" s="1">
         <v>11852.898192500599</v>
       </c>
-      <c r="J27" s="1">
+      <c r="O27" s="2">
+        <v>61364</v>
+      </c>
+      <c r="P27" s="1">
         <v>34551.895088555597</v>
       </c>
-      <c r="K27" s="1">
+      <c r="Q27" s="1">
         <v>23867.2419793607</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>2</v>
       </c>
@@ -3417,29 +4876,44 @@
       <c r="C28" t="s">
         <v>0</v>
       </c>
-      <c r="E28" s="1">
+      <c r="F28" s="1">
         <v>4422.61849416733</v>
       </c>
-      <c r="F28" s="1">
+      <c r="G28" s="1">
+        <v>23117.8035483762</v>
+      </c>
+      <c r="H28" s="1">
         <v>40759.000567518902</v>
       </c>
-      <c r="G28" s="1">
-        <v>47209.029960939399</v>
-      </c>
-      <c r="H28" s="1">
+      <c r="I28" s="1">
+        <v>631205.11121523799</v>
+      </c>
+      <c r="J28" s="2">
+        <v>32647.826679738999</v>
+      </c>
+      <c r="K28" s="1">
+        <v>143182.845656399</v>
+      </c>
+      <c r="L28" s="1">
         <v>307.24312553894498</v>
       </c>
-      <c r="I28" s="1">
+      <c r="M28" s="1">
+        <v>155398.245595377</v>
+      </c>
+      <c r="N28" s="1">
         <v>16327.443986461099</v>
       </c>
-      <c r="J28" s="1">
+      <c r="O28" s="2">
+        <v>83513</v>
+      </c>
+      <c r="P28" s="1">
         <v>27665.411221903702</v>
       </c>
-      <c r="K28" s="1">
+      <c r="Q28" s="1">
         <v>19303.870779180601</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>1</v>
       </c>
@@ -3449,27 +4923,46 @@
       <c r="C29" t="s">
         <v>0</v>
       </c>
-      <c r="E29" s="1">
+      <c r="F29" s="1">
         <v>3648.8893564674299</v>
       </c>
-      <c r="F29" s="1">
+      <c r="G29" s="1">
+        <v>15326.350033728801</v>
+      </c>
+      <c r="H29" s="1">
         <v>32994.459846837803</v>
       </c>
-      <c r="G29" s="1">
-        <v>29950.4557205399</v>
-      </c>
-      <c r="H29" s="1">
+      <c r="I29" s="1">
+        <v>409937.75157703902</v>
+      </c>
+      <c r="J29" s="2">
+        <v>22942.881008679298</v>
+      </c>
+      <c r="K29" s="1">
+        <v>78876.747919707894</v>
+      </c>
+      <c r="L29" s="1">
         <v>101.43299458342101</v>
       </c>
-      <c r="I29" s="1">
+      <c r="M29" s="1">
+        <v>90344.625271251003</v>
+      </c>
+      <c r="N29" s="1">
         <v>15031.7875034074</v>
       </c>
-      <c r="J29" s="1">
+      <c r="O29" s="2">
+        <v>79341</v>
+      </c>
+      <c r="P29" s="1">
         <v>16842.1456445771</v>
       </c>
-      <c r="K29" s="1">
+      <c r="Q29" s="1">
         <v>12626.1323890277</v>
       </c>
+    </row>
+    <row r="32" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="J32" s="1"/>
+      <c r="K32" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
